--- a/docs/flight-suggested-questions-gap-analysis.xlsx
+++ b/docs/flight-suggested-questions-gap-analysis.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Skip Scenarios" sheetId="3" r:id="rId3"/>
     <sheet name="Fix Sequence" sheetId="4" r:id="rId4"/>
     <sheet name="Open Decisions" sheetId="5" r:id="rId5"/>
+    <sheet name="Read Me" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -32,42 +33,52 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Production behavior</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Current behavior</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Missing rule / logic</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Impact</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Severity</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Recommended fix direction</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Step</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify by</t>
         </is>
       </c>
     </row>
@@ -89,42 +100,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt.ts:427 "Use at the end of every Flight Agent turn"; :655 "Before final response, always update Flight suggested questions"; :171 stop rule "Perform only the mandatory final suggested-questions update, then respond".</t>
+          <t xml:space="preserve">Production regression</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt.ts:137 "This is optional, best-effort enrichment"; :71 "Optional suggestion enrichment may run once"; agent.ts:229 repeats "Suggested questions are optional".</t>
+          <t xml:space="preserve">Mandatory on every turn. FLIGHT_PROD_PROMPT_TEXT states it in the stop rule (prompt.ts:171 "Perform only the mandatory final suggested-questions update, then respond"), the tools intro (:173), the tool section (:427 "Use at the end of every Flight Agent turn", :431 "call this tool as the final tool call"), the routing tail (:655 "Before final response, always update Flight suggested questions"), the chain table (:660-676), the checklist (:908) and the dynamic block (:987).</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">FLIGHT_PROMPT calls it "optional, best-effort enrichment" (prompt.ts:137) and says "Optional suggestion enrichment may run once" (:71). The dynamic instructions repeat "Suggested questions are optional" (agent.ts:229). Committed HEAD carries the same wording.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Any unconditional statement that the turn is not finished until the tool has run.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43% call rate across 201 recorded turns; 0% on read-only, prediction and no-tool turns.</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t xml:space="preserve">At analysis (2026-10-01): Flight called it on 84 of 114 turns that ran flight_search or apply_filter, and on 2 of 72 turns that ran neither; 86 of 186 Flight turns overall. Current numbers are on the Evidence sheet.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Replace the optional framing in all three live locations with a required-final-step rule.</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Replace the optional framing in all three live locations (prompt.ts:71, prompt.ts:137, agent.ts:229) with a required-final-step rule. Keep "never retry it or let its failure discard a result".</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence: the "Ran neither" row reaches 100% on a fresh run of the scripted conversations.</t>
         </is>
       </c>
     </row>
@@ -146,42 +167,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt.ts:660-676 lists 15 chains, every one terminating in this tool, including "update_flight_suggested_questions alone for missing-info, clarification, source-option, or no-action responses".</t>
+          <t xml:space="preserve">Production regression</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLIGHT_PROMPT contains no chain table at all.</t>
+          <t xml:space="preserve">prompt.ts:660-676 lists 15 approved chains, each ending in this tool, including "update_flight_suggested_questions alone for missing-info, clarification, source-option, or no-action responses" (:662).</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per-request-class sequencing that names the tool as the terminal step.</t>
+          <t xml:space="preserve">FLIGHT_PROMPT has no chain table; the tool section only says to run it "after the core request is complete" (prompt.ts:137).</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The three 0% measured rows map one-to-one onto the missing chains (contract read, prediction, no-tool).</t>
+          <t xml:space="preserve">Per-request-class sequencing that names the tool as the terminal step, including turns that need no core tool.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t xml:space="preserve">At analysis: contract reads 1 of 46, price prediction 0 of 11, Flight turns with no core tool 0 of 13 - the request classes the missing chains covered.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Add a compact chain list ending in the tool; the standalone clarification case matters most (0/12 turns today).</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Port a compact chain list adapted to the five registered tools. Do not copy the six chains that name resolve_flight_date: the tool is not registered (tools/index.ts:59-65) and flight-agent-price-prediction.test.ts:596 asserts FLIGHT_PROMPT never mentions it. Local ranking reads without selecting (prompt.ts:112), so production’s read-then-select chain becomes read only. The standalone chain matters most.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence: the getGeneratedContractsContext, price_prediction_tool and (no tool) rows reach 100%.</t>
         </is>
       </c>
     </row>
@@ -203,42 +234,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t xml:space="preserve">prompt.ts:908 "Did I call update_flight_suggested_questions as the final tool call and avoid mentioning its result to the user?"</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No checklist of any kind in the live prompt.</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t xml:space="preserve">No checklist of any kind in FLIGHT_PROMPT.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">A self-verification pass before the final output is emitted.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">No second chance for the model to notice the omission.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">One checklist line in the "Final response and stopping" section.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A prompt unit test asserts the checklist line.</t>
         </is>
       </c>
     </row>
@@ -255,47 +296,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A clause actively instructs the model to drop it</t>
+          <t xml:space="preserve">A clause tells the model to drop it under budget pressure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn budget was never traded against this tool.</t>
+          <t xml:space="preserve">Local-only</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t xml:space="preserve">The turn budget was never traded against this tool.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">prompt.ts:143 "Search/filter/contract success outranks suggestion enrichment. Prioritize completing structured feedback within the turn budget over optional work."</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">Nothing - this is an added counter-incentive rather than an omission.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">With maxTurns: 10 (config.ts:88) this is the first thing dropped under pressure.</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t xml:space="preserve">With maxTurns 10 (config.ts:88) this is the first work dropped under pressure.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Keep "never let it discard a successful result"; delete the optional-work / budget trade-off framing.</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Keep "never let it discard a successful result"; delete the optional-work and turn-budget trade-off.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A prompt unit test asserts the trade-off is gone; the max-turns recovery test (flight-agent-recovery-loop.test.ts:425) still preserves core results.</t>
         </is>
       </c>
     </row>
@@ -312,47 +363,57 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manager-mode instructions de-escalate it</t>
+          <t xml:space="preserve">Manager mode de-escalates it and sets no order</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The agent ended its turn in free text, so "final tool call before your final text response" was a coherent instruction.</t>
+          <t xml:space="preserve">Production regression</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FlightManagerAgent sets outputType: flightManagerOutputSchema (agent.ts:250) so the turn ends by emitting JSON; manager-output.ts:38 says "Optional suggested-question work never changes a successful core outcome."</t>
+          <t xml:space="preserve">The agent ended its turn in free text, so "call this tool as the final tool call before your final text response" (prompt.ts:431) was a coherent instruction.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t xml:space="preserve">FlightManagerAgent sets outputType: flightManagerOutputSchema (agent.ts:250), so the turn ends by emitting structured output, and manager-output.ts:38 says "Optional suggested-question work never changes a successful core outcome." All chat API traffic takes this path (manager-orchestrator/runner.ts), and so did every recorded artifact, including the scripted conversations.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve">An ordering rule: tool call first, structured output second.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manager-path call rates of 43% (manager-flight-*) and 35% (manager-realistic-*).</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t xml:space="preserve">At analysis: 86 of 186 Flight turns, all on the Manager path (45% for manager-flight-*, 38% for manager-realistic-*). There is no standalone-runner evidence to compare against.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">State the ordering in FLIGHT_MANAGER_INSTRUCTIONS and drop the de-escalation sentence. Do NOT add a schema field - the consumer reads shared context, not Manager feedback.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence: every Manager-path Flight turn calls the tool.</t>
         </is>
       </c>
     </row>
@@ -374,42 +435,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A "Required behavior" block: call it as the final tool call before the final text response.</t>
+          <t xml:space="preserve">Production regression</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">suggested-questions-tool.ts:84 "Best-effort enrichment after the user’s core Flight request is complete..."</t>
+          <t xml:space="preserve">The tool section’s "Required behavior": call it as the final tool call before the final text response, at most once, then no more tools (prompt.ts:429-433).</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Required/terminal framing in the text the model receives alongside the tool schema.</t>
+          <t xml:space="preserve">UpdateFlightSuggestedQuestionsTool description (suggested-questions-tool.ts:94): "Best-effort enrichment after the user’s core Flight request is complete..."</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Required, terminal framing in the text the model receives alongside the tool schema.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t xml:space="preserve">The description ships in the same payload as the prompt and will undercut G1.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mirror the trip-planner sibling: "Call only after context capture and all planning tools, as the final tool call." (trip-planner/tools/context-tools.ts:205-206)</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mirror the Trip Planner sibling: "Call only after context capture and all planning tools, as the final tool call." (trip-planner/tools/context-tools.ts:205-206)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A unit test asserts the description calls it the final tool call.</t>
         </is>
       </c>
     </row>
@@ -426,47 +497,57 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schema admits a payload that can only fail</t>
+          <t xml:space="preserve">Schema admits payloads that can only fail</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Shared weakness</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t xml:space="preserve">"Exactly 3" was prose only, same as here.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">suggested-questions-tool.ts:16-23 uses .array(z.string().min(1)).max(3) with no .min(3). The provider sees maxItems: 3 and no minimum, so a 1-2 item array is schema-valid, reaches execute, and is rejected with INVALID_SUGGESTED_QUESTIONS / retrySafe: false (:58-71). isEnabled (:91-96) then hides the tool for the rest of the turn.</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A schema that can express both valid states and nothing else.</t>
+          <t xml:space="preserve">updateFlightSuggestedQuestionsSchema (suggested-questions-tool.ts:26-33) is .array(z.string().min(1)).max(3) with no .min(3). A 1-2 item array, or an empty array while a search key exists, is schema-valid, reaches execute and is rejected with INVALID_SUGGESTED_QUESTIONS and retrySafe: false (:59-81). isEnabled (:101-106) then hides the tool for the rest of the request.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dead-end failure mode - one malformed draft and the turn stores nothing, with no retry path. Already exercised at flight-agent-recovery-loop.test.ts:315-317.</t>
+          <t xml:space="preserve">A schema that can express the valid states and nothing else.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t xml:space="preserve">A dead end: one malformed draft and the turn stores nothing, with no retry path. Not seen in any recorded turn; exercised by flight-agent-recovery-loop.test.ts:315-330.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DECISION NEEDED. A plain .min(3) is wrong: the empty array is how "no active search, clear stale suggestions" is expressed (:41-47). Option (a) keep 0..3 plus a clearOnly discriminator; option (b) PREFERRED .min(3).max(3) like trip-planner (context-tools.ts:116-123) and move clearing into the Step 1 finalize. Also consider per-string .max(80).</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve">DECISION NEEDED. A plain .min(3) is wrong while the empty array is how "no active search, clear stale suggestions" is expressed (:46-57). Option (a): keep 0..3 plus a clearOnly discriminator. Option (b), PREFERRED: .min(3).max(3) like Trip Planner (context-tools.ts:116-123), with clearing moved into the Step 1 finalize. Also consider a per-string .max(80).</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit tests: the schema rejects 1-2 items before execute, and the no-search path still clears.</t>
         </is>
       </c>
     </row>
@@ -483,47 +564,57 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">No phase gate; "at most once" is the only constraint</t>
+          <t xml:space="preserve">No phase gate and no retry; "at most once" is the only constraint</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">"After it returns successfully, call no more tools", and never before core work.</t>
+          <t xml:space="preserve">Shared weakness</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">isEnabled dedupes by requestId only (suggested-questions-tool.ts:91-96). It does not require core work to be complete and does not stop later tool calls.</t>
+          <t xml:space="preserve">Phase rules lived in the prompt: never before core work, and "After it returns successfully, call no more tools" (prompt.ts:433).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">A turn-phase gate.</t>
+          <t xml:space="preserve">isEnabled (suggested-questions-tool.ts:101-106) hides the tool once it has run for the current requestId, whether the call succeeded or failed. Nothing stops later tool calls, and a rejected draft cannot be retried.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">The tool can fire mid-turn; nothing guarantees it is last.</t>
+          <t xml:space="preserve">A per-turn gate that allows one retry after a rejected draft and reopens the tool when results change after it ran.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t xml:space="preserve">One bad draft ends the turn with no suggestions. A search or filter after the call leaves new results with suggestions written for the old ones (HEAD) or none (working tree).</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mirror the trip-planner gate (context-tools.ts:209-216: contextCaptured &amp;&amp; !suggestionsUpdated &amp;&amp; attempts &lt; 2), adapted to "core work complete".</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gate on per-run turn state: at most two attempts, closed once written, reopened when flight_search or apply_filter runs after the write. Unlike Trip Planner (context-tools.ts:209-216), Flight has no mandatory first step, so "core work complete" cannot be computed - do not gate on it, and do not disable core tools after the write.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit tests: a rejected draft can be retried once, and a search after the write reopens the tool.</t>
         </is>
       </c>
     </row>
@@ -540,47 +631,57 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">A skipped call silently keeps last turn’s suggestions</t>
+          <t xml:space="preserve">A skipped call keeps the previous turn’s suggestions</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">The tool was mandatory and re-read searchKey at execution time, so every turn ended in a deliberate write.</t>
+          <t xml:space="preserve">Shared weakness</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">prepareFlightAgentTurnContext clears only when there is no searchKey (flight-context.ts:345-347). On a read-only turn with an active search and no tool call, the previous turn’s three strings persist verbatim.</t>
+          <t xml:space="preserve">Every turn ended in a deliberate write: the tool was mandatory and re-read searchKey at execution time (prompt.ts:437-441).</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">An end-of-turn finalize. The sibling has exactly this: finalizeTripPlannerTurn clears when !turnState.suggestionsUpdated (trip-planner/context/lifecycle.ts:422-425); trip-planner/runner.ts:434 clears on error.</t>
+          <t xml:space="preserve">Committed HEAD never clears suggestions outside the tool, so a skipped call ships the previous turn’s strings even after a new search. The working tree adds a turn-start clear only when there is no search key (flight-context.ts:345-347, uncommitted), so with an active search a skipped read-only turn still ships the previous strings. An uncommitted, untested draft adds finalizeFlightSuggestedQuestions (suggested-questions-tool.ts:150-166), called from runner.ts:170 and :197 and from manager/specialists/flight.ts:24-32. On the Manager path it does not run when the nested Flight run throws, because customOutputExtractor is skipped.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silent staleness, invisible to tests - the lenient live assertions check suggestions.length === 3 (flight-agent-intelligence-deep-chats-live.ts:789-801), which passes on stale data.</t>
+          <t xml:space="preserve">A turn-end finalize on every path plus a per-turn written flag. Trip Planner has both: finalizeTripPlannerTurn clears when !turnState.suggestionsUpdated (trip-planner/context/lifecycle.ts:423-425), and trip-planner/runner.ts:434 clears on error.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Silent staleness, invisible to tests: the deep-chats live check only asserts suggestions.length === 3 (flight-agent-intelligence-deep-chats-live.ts:798), which stale data passes.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Add a flight turn-finalize plus a per-turn suggestionsUpdated flag. Correct regardless of the mandate decision, so do it first.</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Keep the finalize, cover the Manager error path, and add tests. First decide whether a skipped read-only turn should clear or keep its suggestions: clearing turns stale-but-same-search suggestions into none, so land Step 1 with or just before Steps 2-3.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - uncommitted draft in working tree, untested</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit tests: with an active search and no tool call, no previous strings survive the turn; the finalize also runs when Flight throws on the Manager path.</t>
         </is>
       </c>
     </row>
@@ -597,47 +698,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mutation tools wipe without refill</t>
+          <t xml:space="preserve">Search and filter invalidate suggestions, but nothing guarantees a refill</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same clearing, but the mandated end-of-turn write always refilled.</t>
+          <t xml:space="preserve">Local-only</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">search-tool.ts:482 and filter/tool.ts:183 set suggestedQuestions = []; see the Evidence sheet for the count of turns that never refilled.</t>
+          <t xml:space="preserve">The mandated end-of-turn write replaced the suggestions whenever results changed.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t xml:space="preserve">The working tree adds clearing to flight_search (search-tool.ts:482) and apply_filter (filter/tool.ts:183), both uncommitted; committed HEAD does not clear there. Either way nothing guarantees a refresh: the Evidence sheet counts the search/filter turns that ended without one.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t xml:space="preserve">The guaranteed refill, not the clearing.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Empty suggestion chips after a search or filter - the most user-visible symptom.</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t xml:space="preserve">At analysis: 30 of 114 result-changing Flight turns ended without a refresh. With the working-tree code they ship no suggestions; with HEAD they ship suggestions written for the previous results - the most user-visible symptom.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Keep the clearing (it is correct invalidation) and close the hole via G1/G8/G9.</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Keep the clearing (it is correct invalidation) and close the hole through G1, G6, G8 and G9.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - the clearing is uncommitted working-tree code</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence: "Search/filter turns with no refresh" reaches 0.</t>
         </is>
       </c>
     </row>
@@ -659,42 +770,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prompt-level only there too, but the prompt said "mandatory".</t>
+          <t xml:space="preserve">Shared weakness</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">toolChoice: ‘auto’ (config.ts:19-22); no output guardrail on the agent (agent.ts:234-240); no post-run inspection of toolCallLog in runner.ts:154-185; the max-turns recovery path deliberately excludes it from CORE_TOOLS (recovery-outcome.ts:6-10).</t>
+          <t xml:space="preserve">Prompt-level only there too, but the prompt said mandatory.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t xml:space="preserve">toolChoice: auto (config.ts:19-22); no output guardrail on the Flight agent (agent.ts:234-251); the max-turns recovery path deliberately leaves the tool out of CORE_TOOLS (recovery-outcome.ts:6-10). The only post-run hook is the uncommitted finalize draft (G9).</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Any mechanism that notices the omission.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The prompt is the sole control, and it currently says "optional".</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t xml:space="preserve">The prompt is the sole control, and it currently says optional.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The G9 finalize is the enforcement point. Keep toolChoice: auto - forcing a specific tool would break the core tool loop.</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Make the G9 finalize the enforcement point. Keep toolChoice: auto - forcing a specific tool would break the core tool loop.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - uncommitted draft in working tree, untested</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Covered by the G9 tests.</t>
         </is>
       </c>
     </row>
@@ -716,42 +837,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Local-only</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t xml:space="preserve">n/a - this is local test debt.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NON_CORE_TOOLS strips the tool before scoring, rationale "must never decide a pass or fail" (flight-agent-conversation-cases.ts:26-27,53). flight-gap-contracts.test.ts:59 is named for the absence. In the report harness none of the 17 expectedTools arrays include it and validateTurn compares tool sequences by exact string equality (flight-agent-session-complex-report-live.ts:434-440). The one script that requires the call (flight-agent-suggested-questions-variation-live.ts:146-148) has no npm script and is never run.</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t xml:space="preserve">flight-agent-price-prediction.test.ts:609-612 asserts FLIGHT_PROMPT contains "optional, best-effort", and :596 asserts it never names resolve_flight_date. NON_CORE_TOOLS strips the tool before scoring because it "must never decide a pass or fail" (flight-agent-conversation-cases.ts:26-27, 53). The untracked flight-gap-contracts.test.ts:59 is named for its absence. In the report harness none of the 17 expectedTools arrays include it, and validateTurn compares tool sequences by exact string equality (flight-agent-session-complex-report-live.ts:435-442). The one live script that requires the call (flight-agent-suggested-questions-variation-live.ts:146-148) has no npm script and is never run.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Expectations that encode the mandate rather than its absence.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Restoring the mandate turns the report harness red on every turn before it turns anything green.</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Restoring the mandate turns the unit suite and the report harness red before it turns anything green.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flip the expectations as part of the change, not after it.</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Flip the expectations in the same change as Step 3, not after it.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">npm test passes with the mandate in place, and the report harness expects the tool on every turn.</t>
         </is>
       </c>
     </row>
@@ -773,42 +904,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Shared weakness</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t xml:space="preserve">n/a</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.debug/flight-prompt-traces is metadata-only (captureMode "safe"; 61 files, 3 with modelCalls, 0 tool-call records). flight_agent.response (runner.ts:170-176) logs nothing about suggestions.</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">A per-turn record of whether the tool ran.</t>
+          <t xml:space="preserve">.debug/flight-prompt-traces is metadata-only (61 files, no tool-call records). The uncommitted draft logs suggestedQuestionCount and staleSuggestionsCleared in flight_agent.response (runner.ts:172-183), but only in the standalone runner. The Manager path, which carries every chat API turn and every recorded artifact, logs nothing about suggestions.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t xml:space="preserve">A per-turn record of whether the tool ran, on the path production traffic takes.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t xml:space="preserve">The call rate is unmeasurable in a running system; this gap was only visible by grepping recorded artifacts.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Log suggestionsUpdated and the suggestion count per turn.</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Log whether suggestions were written or cleared, and how many, from the Manager-path finalize as well as the standalone runner.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open</t>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - uncommitted draft logs only on the standalone path</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Manager-path Flight turn emits the log line.</t>
         </is>
       </c>
     </row>
@@ -830,42 +971,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Local-only</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t xml:space="preserve">n/a</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flight-agent-recent-changes.md:251, flight-agent-context-flow.md:429, flight-agent-date-handling-multiturn.md:390 and prompts/prompt-with-error.md:232 all state it runs last on every turn. No doc calls it optional.</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t xml:space="preserve">flight-agent-recent-changes.md:251, flight-agent-context-flow.md:429, flight-agent-date-handling-multiturn.md:390 and prompts/prompt-with-error.md:232 all say it runs last on every turn. No doc calls it optional.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Agreement between the docs and the live prompt.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">Anyone reading the docs concludes the rule is already enforced.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Docs become correct once G1-G3 land; add the chain list and note that FLIGHT_PROD_PROMPT_TEXT is dead text.</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">The docs become correct once Step 3 lands; add the chain list and note that FLIGHT_PROD_PROMPT_TEXT is reference text that never reaches the model.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Step 5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doc review against the shipped prompt.</t>
         </is>
       </c>
     </row>
@@ -886,7 +1037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 2026-10-01T09:36:30.585Z</t>
+          <t xml:space="preserve">Generated: 2026-10-01T10:23:28.975Z</t>
         </is>
       </c>
     </row>
@@ -900,365 +1051,335 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Method: per recorded turn, read the tool list (rawTools, else flightTools, else actualTools) and check whether it contains update_flight_suggested_questions. "Cleared not refilled" counts turns where flight_search or apply_filter ran - both wipe suggestedQuestions - and the tool was not called.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t xml:space="preserve">Recorded turns: 201. Turns where Flight ran: 186. Turns the Manager answered without Flight: 15 - excluded below, because Flight never ran and so could not skip the tool. Manager-path turns: 201 of 201.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method: for each Flight turn, read the tool list (rawTools, else flightTools, else actualTools) and check whether it contains update_flight_suggested_questions. "Search/filter turns with no refresh" counts turns where flight_search or apply_filter replaced the results and the tool was not called. With the working-tree code those turns end with no suggestions; with committed HEAD they keep suggestions written for the previous results.</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Call rate by core-tool signature - all recorded turns</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Core tools in the turn</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Turns</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool called</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">At analysis (2026-10-01): the recordings come from two prompt eras (manager-flight-five-chats-* and manager-realistic-conversations from 2026-09-19, the rest from 2026-09-30 to 2026-10-01). None reflect the working-tree prompt edited at 14:28 on 2026-10-01, so capture a fresh baseline before Step 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98%</t>
+          <t xml:space="preserve">Call rate by whether the turn changed the results</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">Turns</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">50%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext</t>
+          <t xml:space="preserve">Ran flight_search or apply_filter</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">114</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2%</t>
+          <t xml:space="preserve">74%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no tool)</t>
+          <t xml:space="preserve">Ran neither</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">72</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">price_prediction_tool</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + flight_search</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88%</t>
+          <t xml:space="preserve">Call rate by core-tool signature - all Flight turns</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
+          <t xml:space="preserve">Core tools in the turn</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">50%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search + getGeneratedContractsContext</t>
+          <t xml:space="preserve">flight_search</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">98%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
+          <t xml:space="preserve">apply_filter</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">50%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search + price_prediction_tool</t>
+          <t xml:space="preserve">getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t xml:space="preserve">46</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no tool)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Call rate by core-tool signature - flight-conversation-* fixtures only (the set the fix verification re-runs)</t>
+          <t xml:space="preserve">price_prediction_tool</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core tools in the turn</t>
+          <t xml:space="preserve">apply_filter + flight_search</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turns</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tool called</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate</t>
+          <t xml:space="preserve">88%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter</t>
+          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">72%</t>
+          <t xml:space="preserve">50%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search</t>
+          <t xml:space="preserve">flight_search + getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no tool)</t>
+          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext</t>
+          <t xml:space="preserve">flight_search + price_prediction_tool</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1272,234 +1393,209 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">price_prediction_tool</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">Call rate by core-tool signature - flight-conversation-* scripted conversations only (the set fix verification re-runs)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + flight_search</t>
+          <t xml:space="preserve">Core tools in the turn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
+          <t xml:space="preserve">apply_filter</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+          <t xml:space="preserve">72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight_search</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Call rate by artifact group</t>
+          <t xml:space="preserve">getGeneratedContractsContext</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Group</t>
+          <t xml:space="preserve">(no tool)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turns</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tool called</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cleared not refilled</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight-conversation-*</t>
+          <t xml:space="preserve">price_prediction_tool</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">48%</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">manager-flight-*</t>
+          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">43%</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">manager-realistic-*</t>
+          <t xml:space="preserve">apply_filter + flight_search</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">35%</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOTAL</t>
+          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">43%</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
@@ -1507,14 +1603,182 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Target after the fix</t>
+          <t xml:space="preserve">Call rate by artifact group</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every core-tool signature row reaches 100%, including getGeneratedContractsContext, price_prediction_tool and (no tool) - the three that are effectively never called today - and "Cleared not refilled" reaches 0.</t>
+          <t xml:space="preserve">Group</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recorded turns</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flight turns</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tool called</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search/filter turns with no refresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight-conversation-*</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53%</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manager-flight-*</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manager-realistic-*</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38%</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target after the fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every core-tool signature row reaches 100%, including getGeneratedContractsContext, price_prediction_tool and (no tool), and "Search/filter turns with no refresh" reaches 0.</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1797,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measured evidence</t>
+          <t xml:space="preserve">Evidence (measured rows are re-tallied on every run)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1545,17 +1809,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Informational question about current options</t>
+          <t xml:space="preserve">Informational or ranking question about current options</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 of 11 turns called the tool</t>
+          <t xml:space="preserve">All Flight turns: 1 of 46 called it. Scripted conversations: 0 of 11.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No chain covers getGeneratedContractsContext, and no mutation tool ran, so the "when called with an active search" wording never clearly applies.</t>
+          <t xml:space="preserve">No chain covers a contract read and no search or filter ran, so the "when called with an active search" wording never clearly applies.</t>
         </is>
       </c>
     </row>
@@ -1567,29 +1831,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 of 5 turns</t>
+          <t xml:space="preserve">All Flight turns: 0 of 11 called it. Scripted conversations: 0 of 5.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same - prompt.ts:672-676 chains exist only in the dead reference text.</t>
+          <t xml:space="preserve">The prediction chains exist only in FLIGHT_PROD_PROMPT_TEXT (prompt.ts:672-676).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clarification / missing-info turn with no tools</t>
+          <t xml:space="preserve">Clarification, missing-info or source-option answer with no core tool</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 of 12 turns</t>
+          <t xml:space="preserve">All Flight turns: 0 of 13 called it. Scripted conversations: 0 of 5.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production had an explicit standalone chain for exactly this case; the local prompt has none.</t>
+          <t xml:space="preserve">Production had a standalone chain for exactly this case (prompt.ts:662); the local prompt has none.</t>
         </is>
       </c>
     </row>
@@ -1601,61 +1865,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipped on 5 of 18 turns</t>
+          <t xml:space="preserve">All Flight turns: 25 of 50 called it. Scripted conversations: 13 of 18.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called opportunistically, not reliably.</t>
+          <t xml:space="preserve">Called opportunistically, not reliably. The skips are spread across ordinary filter additions, not just resets.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Under turn-budget pressure</t>
+          <t xml:space="preserve">Search turn (for comparison)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">licensed by prompt.ts:143</t>
+          <t xml:space="preserve">All Flight turns: 51 of 52 called it. Scripted conversations: 16 of 16.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The prompt tells the model to prioritise structured feedback over "optional work".</t>
+          <t xml:space="preserve">The one case the model handles reliably: it treats the tool as a refresh after new results, not as the end of every turn.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manager mode</t>
+          <t xml:space="preserve">Under turn-budget pressure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">43% and 35% call rates</t>
+          <t xml:space="preserve">Licensed by prompt.ts:143.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The turn ends by emitting the structured output, and manager-output.ts:38 explicitly calls the work optional.</t>
+          <t xml:space="preserve">The prompt tells the model to prioritise structured feedback over "optional work".</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Manager mode</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201 of 201 recorded turns ran on the Manager path.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The turn ends by emitting structured output, and manager-output.ts:38 explicitly calls the work optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Non-deterministically, on identical input</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">search_filter_options turn 2 "Show nonstop flights only" - called in manager-flight-five-chats-live.json, not called in the byte-identical -traced-live.json</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">search_filter_options turn 2, "Show nonstop flights only.": called in manager-flight-five-chats-live.json, not called in manager-flight-five-chats-traced-live.json.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">Nothing enforces it, so it is left to sampling.</t>
         </is>
@@ -1720,7 +2001,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deterministic state correctness: suggestionsUpdated flag, flight turn finalize on success and error paths, per-turn logging</t>
+          <t xml:space="preserve">Deterministic state correctness: per-turn written flag, turn-end finalize on the success and error paths of both the standalone and Manager runs, per-turn logging on the Manager path</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1730,7 +2011,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correct on its own merits and independent of the mandate decision. After this, a skipped call can no longer ship stale data.</t>
+          <t xml:space="preserve">Correct on its own merits and independent of the mandate decision: after this, a skipped call can no longer ship stale data. Shipped alone it leaves no suggestions on most read-only turns, so land it with or just before Steps 2-3.</t>
         </is>
       </c>
     </row>
@@ -1742,7 +2023,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tool contract: required-terminal description, schema decision, isEnabled phase gate</t>
+          <t xml:space="preserve">Tool contract: required-terminal description, schema decision, per-run gate with one retry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1764,7 +2045,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prompt authority: mandate wording, stop rule, chain list, checklist line, Manager-mode ordering</t>
+          <t xml:space="preserve">Prompt authority: mandate wording, stop rule, adapted chain list, checklist line, Manager-mode ordering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1786,7 +2067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tests: invert NON_CORE_TOOLS, rewrite flight-gap-contracts case, add the tool to the 17 expectedTools arrays, add the missing npm script</t>
+          <t xml:space="preserve">Tests: flip flight-agent-price-prediction.test.ts:609-612, invert NON_CORE_TOOLS, rewrite the flight-gap-contracts case, add the tool to the 17 expectedTools arrays, add an npm script for the variation live check</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1796,7 +2077,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Must land with Step 3 - the report harness compares tool sequences by exact equality and would otherwise fail every turn.</t>
+          <t xml:space="preserve">Must land with Step 3: the unit suite asserts the optional wording, and the report harness compares tool sequences by exact equality.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +2135,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context.flight.suggestedQuestions is persisted and emitted in the SSE done.flightContext payload (api/chat/orchestrator.ts:228), but public/ has zero references to "suggest" and the dashboard reads only showFlight and searchResults. The only reader today is the Flight agent’s own next-turn prompt (agent.ts:109-116), as anti-staleness input. Restoring the mandate buys production parity and correct state plus ~1 extra model call per turn, but no user-visible change until a renderer exists.</t>
+          <t xml:space="preserve">context.flight.suggestedQuestions is persisted with the chat’s runtime context (api/chat/orchestrator.ts:191) and emitted in the SSE done.flightContext payload (:228). public/chat-dashboard reads flightContext for showFlight and searchResults but has zero references to suggestions. The only in-repo reader is the Flight agent’s own next-turn prompt (agent.ts:109-116, 212-214), as anti-repeat input. Restoring the mandate buys production parity and correct state plus about one extra model call per Flight turn, but no user-visible change until a renderer exists.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1871,7 +2152,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plain .min(3) breaks the empty-array clear path. Option (b) - exactly 3 at the schema level, clearing moved to the Step 1 finalize - is preferred.</t>
+          <t xml:space="preserve">A plain .min(3) breaks the empty-array clear path. Option (b) - exactly 3 at the schema level, clearing moved to the Step 1 finalize - is preferred.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1888,12 +2169,103 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT (prompt.ts:148-995) carries all the mandatory language, is commented "Historical comparison reference only; never included in runtime instructions" (:147) and has zero references in src/, tests/ or scripts/. agent.ts:11 imports only FLIGHT_PROMPT. scripts/audit-session-prompts.ts:58 states the invariant: "FLIGHT_PROMPT is the single authoritative runtime prompt."</t>
+          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT (prompt.ts:148-995) carries all the mandatory language. It is commented "Historical comparison reference only; never included in runtime instructions" (:147), exists only in the uncommitted working tree, and no runtime or test code imports it: agent.ts:11 imports only FLIGHT_PROMPT. Lines 914-995 are a captured production dynamic block. scripts/audit-session-prompts.ts:58 states the invariant: "FLIGHT_PROMPT is the single authoritative runtime prompt."</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">Resolved - do not edit that string; every rule must land in the live prompt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What this is</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracking register for the update_flight_suggested_questions gap between production (FLIGHT_PROD_PROMPT_TEXT, src/agents/flight/prompt.ts:148-995, reference text that never reaches the model) and the local Flight Agent (FLIGHT_PROMPT, the dynamic instructions in agent.ts, the tool, and both runners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How to update</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit scripts/write-suggested-questions-gap-register.ts, then run npm run gaps:suggested-questions. The generator rewrites this workbook, so edits made here are lost. When a fix lands, change that gap’s status in the generator and commit the generator and the workbook together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Line numbers</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measurements</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uncommitted work</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G9, G10, G11 and G13 refer to code that exists only in the uncommitted working tree. Nothing in this register is approved for implementation yet.</t>
         </is>
       </c>
     </row>

--- a/docs/flight-suggested-questions-gap-analysis.xlsx
+++ b/docs/flight-suggested-questions-gap-analysis.xlsx
@@ -5,9 +5,11 @@
     <sheet name="Gap Register" sheetId="1" r:id="rId1"/>
     <sheet name="Evidence" sheetId="2" r:id="rId2"/>
     <sheet name="Skip Scenarios" sheetId="3" r:id="rId3"/>
-    <sheet name="Fix Sequence" sheetId="4" r:id="rId4"/>
-    <sheet name="Open Decisions" sheetId="5" r:id="rId5"/>
-    <sheet name="Read Me" sheetId="6" r:id="rId6"/>
+    <sheet name="Production Map" sheetId="4" r:id="rId4"/>
+    <sheet name="Chain Map" sheetId="5" r:id="rId5"/>
+    <sheet name="Fix Sequence" sheetId="6" r:id="rId6"/>
+    <sheet name="Open Decisions" sheetId="7" r:id="rId7"/>
+    <sheet name="Read Me" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -105,7 +107,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandatory on every turn. FLIGHT_PROD_PROMPT_TEXT states it in the stop rule (prompt.ts:171 "Perform only the mandatory final suggested-questions update, then respond"), the tools intro (:173), the tool section (:427 "Use at the end of every Flight Agent turn", :431 "call this tool as the final tool call"), the routing tail (:655 "Before final response, always update Flight suggested questions"), the chain table (:660-676), the checklist (:908) and the dynamic block (:987).</t>
+          <t xml:space="preserve">Mandatory on every turn. FLIGHT_PROD_PROMPT_TEXT states it in the stop rule (prompt.ts:171 "Perform only the mandatory final suggested-questions update, then respond"), the tools intro (:173), the tool section (:427 "Use at the end of every Flight Agent turn", :431 "call this tool as the final tool call"), the routing tail (:655 "Before final response, always update Flight suggested questions"), the chain table (:660-676), the checklist (:908) and the dynamic block (:987). The Production Map sheet lists each one beside its local equivalent.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -197,7 +199,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Port a compact chain list adapted to the five registered tools. Do not copy the six chains that name resolve_flight_date: the tool is not registered (tools/index.ts:59-65) and flight-agent-price-prediction.test.ts:596 asserts FLIGHT_PROMPT never mentions it. Local ranking reads without selecting (prompt.ts:112), so production’s read-then-select chain becomes read only. The standalone chain matters most.</t>
+          <t xml:space="preserve">Port a compact chain list adapted to the five registered tools. Do not copy the six chains that name resolve_flight_date: the tool is not registered (tools/index.ts:59-65) and flight-agent-price-prediction.test.ts:596 asserts FLIGHT_PROMPT never mentions it. Local ranking reads without selecting (prompt.ts:112), so production’s read-then-select chain becomes read only. The standalone chain matters most. The Chain Map sheet gives the adapted list.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1017,6 +1019,274 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Doc review against the shipped prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - Prompt authority</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suggestion-quality rules dropped</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suggestions are user-side actions "shown under You might ask" (prompt.ts:454), with no assistant-style wording such as "Would you like", "Do you want" or "Should I" (:456). They never ask to add or change departure location, arrival location, travel or return dates, with block examples (:458-460). The reply never mentions the tool, its output or the suggestions (:445, :725). Intents rotate across cabin, passengers, trip type, filters and result reasoning (:472).</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLIGHT_PROMPT keeps a condensed subset (prompt.ts:139): three distinct, context-aware suggestions; no completed or failed action; no active filter; no mandatory route or date fields; never the same three; vary intent. agent.ts:209-210 covers active filters. The voice rule, the never-mention rule and the block examples are gone.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The user-voice rule, the assistant-style ban, the never-mention rule and the block examples.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Once the call rate rises, assistant-voice suggestions can reach the UI, and a standalone reply can mention them. The deep-chats live check still asserts the voice and mandatory-field rules the prompt no longer states (flight-agent-intelligence-deep-chats-live.ts:803-804).</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restore a compact content block of four or five lines in the tool section, worded for both standalone and Manager mode.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 3</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A prompt unit test asserts the rules, and the deep-chats live check passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - Tool definition</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content rules are enforced only by the prompt</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared weakness</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prompt-only there too: "a tool call with the exact same suggestedQuestions array as Previous suggested questions is invalid" (prompt.ts:990) was never checked in code.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updateFlightSuggestedQuestions stores any three non-empty strings (suggested-questions-tool.ts:68-88), including an exact repeat of the previous set or assistant-voice text.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code-level validation. Trip Planner has it: validateTripPlannerSuggestedQuestions checks against the previous set, and a failure returns INVALID_SUGGESTIONS with "retry once" (trip-planner/context/lifecycle.ts:368-385).</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The anti-repeat and voice rules depend on sampling.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optional: a small validator for exact repeats of the previous set, assistant-style openers, mandatory-field wording and length, returning a retryable failure under the G8 gate.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit tests for each rejected case and for the retry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C - State / context</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The once-per-request gate spans the whole Manager turn</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local-only</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One agent turn was one request, so "at most once per turn" and "at most once per request" meant the same thing.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Manager sets one requestId for the whole Manager turn and prepares Flight context once (manager-orchestrator/runner.ts:107, :115). isEnabled (suggested-questions-tool.ts:101-106) and the draft finalize key on that id, so a second flight_agent call in the same Manager turn finds the tool hidden, even after a new search cleared the suggestions.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turn state for each Flight run. Trip Planner resets its turnState at the start of every turn (trip-planner/context/lifecycle.ts:151-175).</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latent: no recorded turn lists more than one Flight subtask or Flight result. When it happens, the second Flight run cannot refresh suggestions.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reset a Flight turn state at the start of every Flight run, on both the Manager and standalone paths, and gate on it instead of the requestId.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integration test: two Flight calls in one Manager turn both refresh suggestions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C - State / context</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Active search" is not tied to the signal the tool uses</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dynamic prompt stated "Active search exists: yes" (prompt.ts:920) and bound the rule to it: three suggestions when yes, an empty array when no (:987, :994). A clarification turn with a search key still got three (:449).</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dynamic prompt shows only "Hydrated search key present (not validated)" (agent.ts:189), and FLIGHT_PROMPT says apply_filter needs "a valid active search, not merely a hydrated search key" (prompt.ts:67). The rule itself says "When called with an active search" (:139). The tool decides on any non-empty searchKey string (suggested-questions-tool.ts:46-57).</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One unambiguous binding to the tool’s own signal, including a search created earlier in the same turn.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The model can judge that no active search exists and send an empty array while a key is present; the tool rejects it and hides itself (G7). Latent: not seen in recorded turns.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One sentence: if a search key exists after this turn’s tools, pass exactly three suggestions; otherwise pass an empty array. Say that clarification turns with a search key also get three.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scripted test: a hydrated key plus a clarification turn stores three suggestions.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1307,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 2026-10-01T10:23:28.975Z</t>
+          <t xml:space="preserve">Generated: 2026-10-01T10:26:42.148Z</t>
         </is>
       </c>
     </row>
@@ -1942,6 +2212,91 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After a rejected draft</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test-only: flight-agent-recovery-loop.test.ts:315-330. No recorded turn hit it.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">isEnabled hides the tool for the rest of the request after any attempt, so a one- or two-item draft can never be corrected (G7, G8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Second Flight call in one Manager turn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latent: no recorded turn lists more than one Flight subtask or Flight result.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One requestId covers the whole Manager turn, so the second Flight run finds the tool hidden, even after a new search cleared the suggestions (G17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hydrated but unvalidated search key</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latent: not seen in recorded turns.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The prompt separates a hydrated key from a valid active search. An empty array sent while a key exists is rejected, and the tool hides itself (G18, G7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run error or max turns</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not recorded separately.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The run ends before the tool is reached, and the max-turns recovery path leaves it out of CORE_TOOLS (recovery-outcome.ts:6-10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manager answers without calling Flight</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 of 201 recorded turns.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not a Flight skip, so the Evidence sheet excludes these turns. Nothing refreshes or clears the Flight suggestions, and the previous ones go out again (see Open Decisions).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1952,154 +2307,220 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step</t>
+          <t xml:space="preserve">Production location (prompt.ts)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scope</t>
+          <t xml:space="preserve">What production says</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Local equivalent</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gaps</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Why this order</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 0</t>
+          <t xml:space="preserve">:171 - decision process, Stop</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This Excel register + extract the shared XLSX writer into scripts/lib/xlsx-workbook.ts</t>
+          <t xml:space="preserve">"Once the request is satisfied or clarification is required, stop task-tool calls. Perform only the mandatory final suggested-questions update, then respond."</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">prompt.ts:71 "stop core tool calls. Optional suggestion enrichment may run once before final feedback."</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Track the gaps before changing behaviour.</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 1</t>
+          <t xml:space="preserve">:173 - tools intro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deterministic state correctness: per-turn written flag, turn-end finalize on the success and error paths of both the standalone and Manager runs, per-turn logging on the Manager path</t>
+          <t xml:space="preserve">"Do NOT chain tools unnecessarily, except approved flight task chains and the required final update_flight_suggested_questions context update."</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9, G10, G11, G13</t>
+          <t xml:space="preserve">None.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correct on its own merits and independent of the mandate decision: after this, a skipped call can no longer ship stale data. Shipped alone it leaves no suggestions on most read-only turns, so land it with or just before Steps 2-3.</t>
+          <t xml:space="preserve">G1, G2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 2</t>
+          <t xml:space="preserve">:426-449 - tool section E</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tool contract: required-terminal description, schema decision, per-run gate with one retry</t>
+          <t xml:space="preserve">Use at the end of every turn; final tool call before the text response; at most once; no tools after it; reads the latest searchKey at execution time; three suggestions with a key, an empty array without; never mention it; clarification turns still call it.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6, G7, G8</t>
+          <t xml:space="preserve">prompt.ts:135-139 "optional, best-effort enrichment"; at most once; three with an active search, an empty array without.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The tool description must stop contradicting the mandate before the prompt asserts it.</t>
+          <t xml:space="preserve">G1, G6, G18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 3</t>
+          <t xml:space="preserve">:450-481 - suggestion rules</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prompt authority: mandate wording, stop rule, adapted chain list, checklist line, Manager-mode ordering</t>
+          <t xml:space="preserve">User-side "You might ask" voice; no assistant-style wording; no mandatory-field suggestions, with block examples; no failed or just-completed action; never the same three; rotate intents; no active filter, including one applied this turn.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1, G2, G3, G4, G5</t>
+          <t xml:space="preserve">prompt.ts:139 keeps a condensed subset; agent.ts:209-210 covers active filters.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raises the call rate once the state layer is already safe.</t>
+          <t xml:space="preserve">G15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 4</t>
+          <t xml:space="preserve">:655-659 - end of the routing procedure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tests: flip flight-agent-price-prediction.test.ts:609-612, invert NON_CORE_TOOLS, rewrite the flight-gap-contracts case, add the tool to the 17 expectedTools arrays, add an npm script for the variation live check</t>
+          <t xml:space="preserve">"Before final response, always update Flight suggested questions." Call it as the final tool call; it re-checks the latest searchKey; do not expose its result.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">G12</t>
+          <t xml:space="preserve">None.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Must land with Step 3: the unit suite asserts the optional wording, and the report harness compares tool sequences by exact equality.</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 5</t>
+          <t xml:space="preserve">:660-676 - approved chains</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconcile the four docs</t>
+          <t xml:space="preserve">15 chains, every one ending in the tool, including the tool alone for missing-info, clarification, source-option and no-action responses.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">G14</t>
+          <t xml:space="preserve">None. See the Chain Map sheet.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last, once behaviour is settled.</t>
+          <t xml:space="preserve">G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:725 - communication style</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"After update_flight_suggested_questions, do not mention suggested questions."</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:908 - final checklist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Did I call update_flight_suggested_questions as the final tool call and avoid mentioning its result to the user?"</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:914-995 - captured dynamic block</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Active search exists: yes" (:920); the mandate restated at the very end of the prompt (:987-988); compare against previous suggestions and never resend the same three (:989-990); mandatory-field guard (:993); an empty array when there is no active search (:994).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">agent.ts:189 "Hydrated search key present (not validated)"; agent.ts:212-214 lists previous suggestions; agent.ts:229 "Suggested questions are optional."</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G1, G18</t>
         </is>
       </c>
     </row>
@@ -2113,68 +2534,377 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topic</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detail</t>
+          <t xml:space="preserve">Production chain (prompt.ts:660-676)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner / status</t>
+          <t xml:space="preserve">Local chain with the five registered tools</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Port</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who renders the suggestions?</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context.flight.suggestedQuestions is persisted with the chat’s runtime context (api/chat/orchestrator.ts:191) and emitted in the SSE done.flightContext payload (:228). public/chat-dashboard reads flightContext for showFlight and searchResults but has zero references to suggestions. The only in-repo reader is the Flight agent’s own next-turn prompt (agent.ts:109-116, 212-214), as anti-repeat input. Restoring the mandate buys production parity and correct state plus about one extra model call per Flight turn, but no user-visible change until a renderer exists.</t>
+          <t xml:space="preserve">update_flight_suggested_questions alone - missing-info, clarification, source-option or no-action responses</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - confirm the real consumer (presumably the CheapOair mobile client).</t>
+          <t xml:space="preserve">update_flight_suggested_questions alone</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes - the most important row</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7 schema shape</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A plain .min(3) breaks the empty-array clear path. Option (b) - exactly 3 at the schema level, clearing moved to the Step 1 finalize - is preferred.</t>
+          <t xml:space="preserve">resolve_flight_date -&gt; update_flight_suggested_questions - vague timing resolved, route or return timing still missing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - decide before Step 2.</t>
+          <t xml:space="preserve">update_flight_suggested_questions alone: the local prompt derives date ranges from the turn clock</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merge into 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dead reference prompt</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT (prompt.ts:148-995) carries all the mandatory language. It is commented "Historical comparison reference only; never included in runtime instructions" (:147), exists only in the uncommitted working tree, and no runtime or test code imports it: agent.ts:11 imports only FLIGHT_PROMPT. Lines 914-995 are a captured production dynamic block. scripts/audit-session-prompts.ts:58 states the invariant: "FLIGHT_PROMPT is the single authoritative runtime prompt."</t>
+          <t xml:space="preserve">flight_search -&gt; update_flight_suggested_questions - search or search update</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved - do not edit that string; every rule must land in the live prompt.</t>
+          <t xml:space="preserve">Same</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolve_flight_date -&gt; flight_search -&gt; update_flight_suggested_questions - vague-date search</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight_search -&gt; update_flight_suggested_questions</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merge into 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">apply_filter -&gt; update_flight_suggested_questions - filter only</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext(read) -&gt; update_flight_suggested_questions - informational current-option question</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext(select) -&gt; update_flight_suggested_questions - explicit indexed comparison</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext(select or show_all) -&gt; update_flight_suggested_questions, for explicit display requests only; comparisons read (prompt.ts:112)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adapt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext(read) -&gt; getGeneratedContractsContext(select) -&gt; update_flight_suggested_questions - cheapest, best, recommendation, generic comparison</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext(read) -&gt; update_flight_suggested_questions: ranking reads without changing visibility (prompt.ts:112)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adapt - same local chain as 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight_search -&gt; apply_filter -&gt; update_flight_suggested_questions - search plus filter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same; also covers apply_filter returning MISSING_SEARCH, then flight_search, then apply_filter (prompt.ts:123)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolve_flight_date -&gt; flight_search -&gt; apply_filter -&gt; update_flight_suggested_questions - vague-date search plus filter</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight_search -&gt; apply_filter -&gt; update_flight_suggested_questions</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merge into 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price_prediction_tool -&gt; update_flight_suggested_questions - route-based date intelligence</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same, after success or failure on advice-only requests</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolve_flight_date -&gt; price_prediction_tool -&gt; update_flight_suggested_questions - vague-date price intelligence</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price_prediction_tool -&gt; update_flight_suggested_questions</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merge into 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price_prediction_tool -&gt; flight_search -&gt; update_flight_suggested_questions - a successful prediction supplies the date and results were requested</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price_prediction_tool -&gt; flight_search [-&gt; apply_filter] -&gt; update_flight_suggested_questions; also the single fallback search after a failed prediction (prompt.ts:102)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolve_flight_date -&gt; price_prediction_tool -&gt; flight_search -&gt; update_flight_suggested_questions</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">price_prediction_tool -&gt; flight_search -&gt; update_flight_suggested_questions</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merge into 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext -&gt; price_prediction_tool -&gt; update_flight_suggested_questions - price advice about a current option</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">getGeneratedContractsContext(read) -&gt; price_prediction_tool -&gt; update_flight_suggested_questions (prompt.ts:95)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Result</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nine local chains: the tool alone; search; filter; search plus filter; contract read; contract select or show_all; prediction; prediction plus search; contract read plus prediction. Each ends in update_flight_suggested_questions, including after recovery retries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constraint</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Do not name resolve_flight_date in FLIGHT_PROMPT: it is not registered (tools/index.ts:59-65), and flight-agent-price-prediction.test.ts:596 asserts the name is absent.</t>
         </is>
       </c>
     </row>
@@ -2188,84 +2918,422 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topic</t>
+          <t xml:space="preserve">Step</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detail</t>
+          <t xml:space="preserve">Scope</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gaps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why this order</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">What this is</t>
+          <t xml:space="preserve">Step 0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracking register for the update_flight_suggested_questions gap between production (FLIGHT_PROD_PROMPT_TEXT, src/agents/flight/prompt.ts:148-995, reference text that never reaches the model) and the local Flight Agent (FLIGHT_PROMPT, the dynamic instructions in agent.ts, the tool, and both runners).</t>
+          <t xml:space="preserve">This Excel register + extract the shared XLSX writer into scripts/lib/xlsx-workbook.ts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Track the gaps before changing behaviour.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">How to update</t>
+          <t xml:space="preserve">Step 0b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit scripts/write-suggested-questions-gap-register.ts, then run npm run gaps:suggested-questions. The generator rewrites this workbook, so edits made here are lost. When a fix lands, change that gap’s status in the generator and commit the generator and the workbook together.</t>
+          <t xml:space="preserve">Baseline: re-run the ten scripted conversations on the current prompt, then re-run this generator</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No recorded artifact reflects the working-tree prompt, so later steps need a fresh baseline to compare against. Live runs cost API calls.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line numbers</t>
+          <t xml:space="preserve">Step 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
+          <t xml:space="preserve">Deterministic state correctness: per-turn written flag, turn-end finalize on the success and error paths of both the standalone and Manager runs, per-turn logging on the Manager path</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G9, G10, G11, G13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct on its own merits: after this, a skipped call can no longer ship stale data. Decide the read-only skip policy first. Shipped alone it leaves no suggestions on most read-only turns, so land it with or just before Steps 2-3.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measurements</t>
+          <t xml:space="preserve">Step 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
+          <t xml:space="preserve">Tool contract: required-terminal description, schema decision, per-run gate with one retry, per-Flight-run turn state, optional content validator</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G6, G7, G8, G16, G17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tool description must stop contradicting the mandate before the prompt asserts it.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin</t>
+          <t xml:space="preserve">Step 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+          <t xml:space="preserve">Prompt authority: mandate wording, stop rule, adapted chain list, checklist line, Manager-mode ordering, content rules, active-search binding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G1, G2, G3, G4, G5, G15, G18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raises the call rate once the state layer is already safe.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Step 4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tests: flip flight-agent-price-prediction.test.ts:609-612, invert NON_CORE_TOOLS, rewrite the flight-gap-contracts case, add the tool to the 17 expectedTools arrays, add an npm script for the variation live check</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Must land with Step 3: the unit suite asserts the optional wording, and the report harness compares tool sequences by exact equality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reconcile the four docs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last, once behaviour is settled.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner / status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who renders the suggestions?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">context.flight.suggestedQuestions is persisted with the chat’s runtime context (api/chat/orchestrator.ts:191) and emitted in the SSE done.flightContext payload (:228). public/chat-dashboard reads flightContext for showFlight and searchResults but has zero references to suggestions. The only in-repo reader is the Flight agent’s own next-turn prompt (agent.ts:109-116, 212-214), as anti-repeat input. Restoring the mandate buys production parity and correct state plus about one extra model call per Flight turn, but no user-visible change until a renderer exists.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - confirm the real consumer (presumably the CheapOair mobile client).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G7 schema shape</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A plain .min(3) breaks the empty-array clear path. Option (b) - exactly 3 at the schema level, clearing moved to the Step 1 finalize - is preferred.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - decide before Step 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dead reference prompt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT (prompt.ts:148-995) carries all the mandatory language. It is commented "Historical comparison reference only; never included in runtime instructions" (:147), exists only in the uncommitted working tree, and no runtime or test code imports it: agent.ts:11 imports only FLIGHT_PROMPT. Lines 914-995 are a captured production dynamic block. scripts/audit-session-prompts.ts:58 states the invariant: "FLIGHT_PROMPT is the single authoritative runtime prompt."</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved - do not edit that string; every rule must land in the live prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skip policy on read-only turns</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When Flight skips the tool on a turn that ran no search or filter, the previous suggestions still describe the same results. Clearing them, as the draft finalize and Trip Planner do, removes any risk of suggesting what the user just did, but leaves no suggestions on most read-only turns until Steps 2-3 raise the call rate. Keeping them leaves suggestions that can repeat the action just taken.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - decide before Step 1. Recommended: clear, shipped together with Steps 2-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turns where Flight never runs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When the Manager answers without calling flight_agent, nothing touches context.flight.suggestedQuestions, and the previous Flight suggestions go out again in done.flightContext (api/chat/orchestrator.ts:228). They still describe the active search, but not the latest exchange. The Evidence sheet counts these turns separately.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - product decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uncommitted Step 1 draft</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">suggested-questions-tool.ts (writtenRequestIds, finalizeFlightSuggestedQuestions), runner.ts and manager/specialists/flight.ts were edited at 15:31-15:32 on 2026-10-01, after this register was first committed. The draft is uncommitted and untested. Known holes: no finalize when the nested Flight run throws on the Manager path, and logging only in the standalone runner.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - keep it as the Step 1 starting point or discard it. It is not approved work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G16 scope</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production never validated suggestion content in code, so a validator goes beyond parity. It matches Trip Planner, which validates and allows one retry.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - decide before Step 2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What this is</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracking register for the update_flight_suggested_questions gap between production (FLIGHT_PROD_PROMPT_TEXT, src/agents/flight/prompt.ts:148-995, reference text that never reaches the model) and the local Flight Agent (FLIGHT_PROMPT, the dynamic instructions in agent.ts, the tool, and both runners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Fix Sequence: the order to close the gaps. Open Decisions: choices to make before development.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How to update</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit scripts/write-suggested-questions-gap-register.ts, then run npm run gaps:suggested-questions. The generator rewrites this workbook, so edits made here are lost. When a fix lands, change that gap’s status in the generator and commit the generator and the workbook together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Line numbers</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measurements</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Uncommitted work</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G9, G10, G11 and G13 refer to code that exists only in the uncommitted working tree. Nothing in this register is approved for implementation yet.</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G9, G10, G11 and G13 refer to code that exists only in the uncommitted working tree; see Open Decisions. Nothing in this register is approved for implementation yet.</t>
         </is>
       </c>
     </row>

--- a/docs/flight-suggested-questions-gap-analysis.xlsx
+++ b/docs/flight-suggested-questions-gap-analysis.xlsx
@@ -142,7 +142,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -209,7 +209,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033 - kept 0..3 and made the first rejection retryable (see Open Decisions)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silent staleness, invisible to tests: the deep-chats live check only asserts suggestions.length === 3 (flight-agent-intelligence-deep-chats-live.ts:798), which stale data passes.</t>
+          <t xml:space="preserve">Stale suggestions reach the client with no error. Only the deep-chats live check would notice, because it compares each set with the previous turn (flight-agent-intelligence-deep-chats-live.ts:826), and it runs only by hand.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - uncommitted draft in working tree, untested</t>
+          <t xml:space="preserve">Fixed in 73d5033 - the working-tree draft was reworked and committed</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - the clearing is uncommitted working-tree code</t>
+          <t xml:space="preserve">Fixed in 73d5033 - the clearing in flight_search and apply_filter is still uncommitted working-tree code</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - uncommitted draft in working tree, untested</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033, 4dae460 and 488c0e9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - uncommitted draft logs only on the standalone path</t>
+          <t xml:space="preserve">Fixed in 73d5033 - flight_suggestions.turn is logged on both paths</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 488c0e9</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033 - a search or filter reopens the tool, instead of per-run state</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 73d5033</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1307,21 +1307,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 2026-10-01T10:26:42.148Z</t>
+          <t xml:space="preserve">Generated: 2026-10-01T12:21:31.639Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artifact files with recorded turns: 30</t>
+          <t xml:space="preserve">Artifact files with recorded turns: 31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded turns: 201. Turns where Flight ran: 186. Turns the Manager answered without Flight: 15 - excluded below, because Flight never ran and so could not skip the tool. Manager-path turns: 201 of 201.</t>
+          <t xml:space="preserve">Recorded turns: 213. Turns where Flight ran: 194. Turns the Manager answered without Flight: 19 - excluded below, because Flight never ran and so could not skip the tool. Manager-path turns: 213 of 213.</t>
         </is>
       </c>
     </row>
@@ -1335,206 +1335,191 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t xml:space="preserve">After 73d5033 the ten scripted conversations (flight-conversation-*) were re-recorded; manager-flight-* and manager-realistic-* still predate it, so the totals below mix both. The comparison table at the end isolates the scripted runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t xml:space="preserve">At analysis (2026-10-01): the recordings come from two prompt eras (manager-flight-five-chats-* and manager-realistic-conversations from 2026-09-19, the rest from 2026-09-30 to 2026-10-01). None reflect the working-tree prompt edited at 14:28 on 2026-10-01, so capture a fresh baseline before Step 1.</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call rate by whether the turn changed the results</t>
-        </is>
-      </c>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flight turns</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Turns</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool called</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate</t>
+          <t xml:space="preserve">Call rate by whether the turn changed the results</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ran flight_search or apply_filter</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">114</t>
+          <t xml:space="preserve">Turns</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">84</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">74%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ran flight_search or apply_filter</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ran neither</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call rate by core-tool signature - all Flight turns</t>
-        </is>
-      </c>
-    </row>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core tools in the turn</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flight turns</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool called</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate</t>
+          <t xml:space="preserve">Call rate by core-tool signature - all Flight turns</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search</t>
+          <t xml:space="preserve">Core tools in the turn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">98%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter</t>
+          <t xml:space="preserve">flight_search</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">50%</t>
+          <t xml:space="preserve">98%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext</t>
+          <t xml:space="preserve">apply_filter</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2%</t>
+          <t xml:space="preserve">62%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no tool)</t>
+          <t xml:space="preserve">getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">33%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_prediction_tool</t>
+          <t xml:space="preserve">(no tool)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1544,12 +1529,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">27%</t>
         </is>
       </c>
     </row>
@@ -1561,83 +1546,83 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">88%</t>
+          <t xml:space="preserve">89%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
+          <t xml:space="preserve">price_prediction_tool</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">50%</t>
+          <t xml:space="preserve">33%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search + getGeneratedContractsContext</t>
+          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
+          <t xml:space="preserve">flight_search + getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">33%</t>
         </is>
       </c>
     </row>
@@ -1701,17 +1686,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">72%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1708,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1745,17 +1730,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
@@ -1767,17 +1752,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
@@ -1789,34 +1774,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
+          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1833,12 +1818,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1850,7 +1835,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
+          <t xml:space="preserve">flight_search + getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1860,12 +1845,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
@@ -1917,27 +1902,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">58</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">66</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">53%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -2013,27 +1998,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">213</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">186</t>
+          <t xml:space="preserve">194</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">121</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">46%</t>
+          <t xml:space="preserve">62%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2026,173 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Target after the fix</t>
+          <t xml:space="preserve">Before and after 73d5033 - scripted conversations recorded on both sides, Flight turns</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turns that called the tool</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before (artifacts/before-suggestions-mandate)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After (re-recorded runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All Flight turns</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31 of 58 (53%)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64 of 64 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ran flight_search or apply_filter</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31 of 36 (86%)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40 of 40 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ran neither</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 of 22 (0%)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 of 24 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contract read only</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 of 11 (0%)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16 of 16 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Price prediction only</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 of 5 (0%)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 of 3 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No core tool</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 of 5 (0%)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 of 2 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Search/filter turns with no refresh</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turns passing the runner’s suggestions check: the update ran last, with 3 suggestions when a search existed and none otherwise</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">not recorded</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64 of 64</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target after the fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">Every core-tool signature row reaches 100%, including getGeneratedContractsContext, price_prediction_tool and (no tool), and "Search/filter turns with no refresh" reaches 0.</t>
         </is>
@@ -2072,7 +2218,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why the current agent skips it</t>
+          <t xml:space="preserve">Why the agent skipped it before 73d5033</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How it is handled now</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2235,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 1 of 46 called it. Scripted conversations: 0 of 11.</t>
+          <t xml:space="preserve">All Flight turns: 17 of 51 called it. Scripted conversations: 16 of 16.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t xml:space="preserve">No chain covers a contract read and no search or filter ran, so the "when called with an active search" wording never clearly applies.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved chain: getGeneratedContractsContext read, then the update. See the before-and-after table on the Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2257,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 0 of 11 called it. Scripted conversations: 0 of 5.</t>
+          <t xml:space="preserve">All Flight turns: 3 of 9 called it. Scripted conversations: 3 of 3.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">The prediction chains exist only in FLIGHT_PROD_PROMPT_TEXT (prompt.ts:672-676).</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved chains for advice only, advice plus results, and advice about a current option, each ending with the update.</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2279,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 0 of 13 called it. Scripted conversations: 0 of 5.</t>
+          <t xml:space="preserve">All Flight turns: 3 of 11 called it. Scripted conversations: 3 of 3.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">Production had a standalone chain for exactly this case (prompt.ts:662); the local prompt has none.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The update alone: 3 suggestions when a search key exists, an empty array otherwise.</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2301,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 25 of 50 called it. Scripted conversations: 13 of 18.</t>
+          <t xml:space="preserve">All Flight turns: 32 of 52 called it. Scripted conversations: 20 of 20.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">Called opportunistically, not reliably. The skips are spread across ordinary filter additions, not just resets.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved chain: apply_filter, then the update. The suggestions guide covers relaxing the new constraint.</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2323,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 51 of 52 called it. Scripted conversations: 16 of 16.</t>
+          <t xml:space="preserve">All Flight turns: 53 of 54 called it. Scripted conversations: 18 of 18.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">The one case the model handles reliably: it treats the tool as a refresh after new results, not as the end of every turn.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged, and now required rather than habitual.</t>
         </is>
       </c>
     </row>
@@ -2177,6 +2353,11 @@
           <t xml:space="preserve">The prompt tells the model to prioritise structured feedback over "optional work".</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The trade-off clause is gone; the prompt asks for lean core work so the update fits (G4).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2186,12 +2367,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">201 of 201 recorded turns ran on the Manager path.</t>
+          <t xml:space="preserve">213 of 213 recorded turns ran on the Manager path.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">The turn ends by emitting structured output, and manager-output.ts:38 explicitly calls the work optional.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLIGHT_MANAGER_INSTRUCTIONS orders the update before the structured feedback and no longer calls it optional (G5).</t>
         </is>
       </c>
     </row>
@@ -2211,6 +2397,11 @@
           <t xml:space="preserve">Nothing enforces it, so it is left to sampling.</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The mandate removes the choice. If a run still skips, the finalize clears rather than shipping stale suggestions.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2228,6 +2419,11 @@
           <t xml:space="preserve">isEnabled hides the tool for the rest of the request after any attempt, so a one- or two-item draft can never be corrected (G7, G8).</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The first rejection is retry-safe and lists the issues; only a second rejection withdraws the tool (G7, G8).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2245,6 +2441,11 @@
           <t xml:space="preserve">One requestId covers the whole Manager turn, so the second Flight run finds the tool hidden, even after a new search cleared the suggestions (G17).</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A search or filter in the second run reopens the tool; a read-only second run keeps the first run’s suggestions (G17).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2262,6 +2463,11 @@
           <t xml:space="preserve">The prompt separates a hydrated key from a valid active search. An empty array sent while a key exists is rejected, and the tool hides itself (G18, G7).</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dynamic prompt says a present key counts even when not validated, and an empty array sent with a key is now retry-safe (G18).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2279,6 +2485,11 @@
           <t xml:space="preserve">The run ends before the tool is reached, and the max-turns recovery path leaves it out of CORE_TOOLS (recovery-outcome.ts:6-10).</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Both runners finalize on failure: the standalone runner in its catch, the Manager runner in a finally.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2288,12 +2499,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 of 201 recorded turns.</t>
+          <t xml:space="preserve">19 of 213 recorded turns.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">Not a Flight skip, so the Evidence sheet excludes these turns. Nothing refreshes or clears the Flight suggestions, and the previous ones go out again (see Open Decisions).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kept on purpose: the finalize clears only after a Flight run.</t>
         </is>
       </c>
     </row>
@@ -2936,6 +3152,11 @@
           <t xml:space="preserve">Why this order</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2958,6 +3179,11 @@
           <t xml:space="preserve">Track the gaps before changing behaviour.</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 5f32c14, a5de88c and 9f2a010</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2980,6 +3206,11 @@
           <t xml:space="preserve">No recorded artifact reflects the working-tree prompt, so later steps need a fresh baseline to compare against. Live runs cost API calls.</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Replaced by the scripted runs recorded earlier on 2026-10-01, kept in artifacts/before-suggestions-mandate/ (see Evidence)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3002,6 +3233,11 @@
           <t xml:space="preserve">Correct on its own merits: after this, a skipped call can no longer ship stale data. Decide the read-only skip policy first. Shipped alone it leaves no suggestions on most read-only turns, so land it with or just before Steps 2-3.</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033, together with Steps 2-4</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3024,6 +3260,11 @@
           <t xml:space="preserve">The tool description must stop contradicting the mandate before the prompt asserts it.</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3046,6 +3287,11 @@
           <t xml:space="preserve">Raises the call rate once the state layer is already safe.</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3068,6 +3314,11 @@
           <t xml:space="preserve">Must land with Step 3: the unit suite asserts the optional wording, and the report harness compares tool sequences by exact equality.</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033, 4dae460 and 488c0e9</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3088,6 +3339,11 @@
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">Last, once behaviour is settled.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 488c0e9: docs/flight-suggested-questions.md is the current reference</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3401,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - decide before Step 2.</t>
+          <t xml:space="preserve">Resolved in 73d5033 - kept 0..3 and made the first rejection retry-safe instead. The update now runs on every turn, so the empty array stays the no-search signal, and tool feedback corrects a misjudged search state instead of ending the turn. A second rejection withdraws the tool.</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3435,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - decide before Step 1. Recommended: clear, shipped together with Steps 2-3.</t>
+          <t xml:space="preserve">Resolved in 73d5033 - clear, shipped together with the mandate, so a skip leaves no suggestions rather than stale ones.</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3452,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - product decision.</t>
+          <t xml:space="preserve">Resolved in 73d5033 - keep. The finalize clears only after a Flight run; a turn the Manager answers alone leaves the suggestions for the active search. Revisit if the client should hide them on such turns.</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3469,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - keep it as the Step 1 starting point or discard it. It is not approved work.</t>
+          <t xml:space="preserve">Resolved in 73d5033 - reworked and committed: a turn snapshot of the previous suggestions, finalize at the end of the Manager turn in a finally, and an agent_start mark for Flight runs.</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3486,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - decide before Step 2.</t>
+          <t xml:space="preserve">Resolved in 73d5033 - in scope: the tool validates drafts and allows one corrected retry.</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3529,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Fix Sequence: the order to close the gaps. Open Decisions: choices to make before development.</t>
+          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Fix Sequence: the order the gaps were closed in, with commits. Open Decisions: the choices made along the way, and the one still open.</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9, G10, G11 and G13 refer to code that exists only in the uncommitted working tree; see Open Decisions. Nothing in this register is approved for implementation yet.</t>
+          <t xml:space="preserve">Every gap records the commit that closed it in Status. The "Current behavior" column describes the code at analysis time, before those commits. The clearing in flight_search and apply_filter (G10) is still uncommitted working-tree code.</t>
         </is>
       </c>
     </row>

--- a/docs/flight-suggested-questions-gap-analysis.xlsx
+++ b/docs/flight-suggested-questions-gap-analysis.xlsx
@@ -1290,6 +1290,475 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - Prompt authority</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No suggestions before a search exists</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The updated text generates 3 grounded CTAs before any search: "CTAs are allowed before flight_search and do not require a searchKey" (prompt.ts:476). Its state matrix (:526-538) covers each partial state. With departure and arrival but no date it offers "Cheapest this week", "Cheapest next month" and "Cheapest in the next 3 months"; it also covers only the departure known, only the arrival known, and a round trip without return timing. An empty list is only for "No meaningful travel context" (:538).</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suggestions are tied to a search key: without one the update passes an empty array and the tool clears the list (suggested-questions-tool.ts:46-57). The live conversation runner enforces that rule (checkSuggestions in tests/live/flight-agent-conversation-live.ts).</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The pre-search state matrix, and a tool that stores 3 records without a search key.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At analysis: every pre-search Flight turn in the re-recorded scripts ended with none, including "I want to book a flight", "I want to fly to Amsterdam", "from Hyderabad" and a prediction-only turn.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Replace the three-or-empty rule with the state matrix, let the tool store 3 records whatever the search state, and change the live check to require 3 whenever travel context exists.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live: trip_details_one_at_a_time and missing_information_progression store 3 CTAs on every turn with partial context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - Tool definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A failed or empty business result still clears the suggestions</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"A failed, empty, or non-success business tool result ... never justifies []" (prompt.ts:472), and the tool "rejects [] with EMPTY_CTA_NOT_ALLOWED whenever route, date, or search context exists" (:474). A failed prediction pivots to search-timing CTAs (:536).</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A failed first search or a failed prediction leaves no search key, so the update stores none. Zero filter matches already keep 3, because the search key survives.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An EMPTY_CTA_NOT_ALLOWED rejection whenever route, date or search context exists.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The traveler sees no next step exactly when an action failed.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reject an empty array whenever route, date or search context exists, as a retry-safe failure under the existing one-retry gate.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit: an empty draft with a known route is rejected. Live: prediction_unavailable_fallback turn 1 stores 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B - Tool definition</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suggestions are plain strings, not CTA records with intent keys</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tool input is { suggestedQuestions: Array&lt;{ text, intentKey }&gt;, consumedIntentKeys: string[] } (prompt.ts:539), with canonical keys such as price_window:next_month, filter:nonstop and results:cheapest (:521-525). The tool updates context.flight.suggestedQuestions and context.flight.ctaState (:468).</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tool takes suggestedQuestions: string[] and stores only context.flight.suggestedQuestions.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Records with canonical intent keys, stored in a ctaState beside the visible texts.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repeats can be caught only by wording, never by intent: "Cheapest next month" and "Show lowest fares next month" count as different.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change the schema to records. Keep writing the texts to suggestedQuestions for the client, and the records to flight.ctaState.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit: records are stored with their keys, and paraphrases of a blocked key are rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C - State / context</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Used and generated intents are not tracked</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ctaState carries generatedIntentKeys, usedIntentKeys and a phaseFingerprint, shown in the dynamic prompt as "Flight CTA intent state" (prompt.ts:1006-1008). Used intents stay blocked, generated ones while the phase is unchanged (:482-486). The model reports consumedIntentKeys for any CTA the user selected (:480), and the tool rejects repeats with REPEATED_CTA_INTENT and excludeIntentKeys (:488).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The only memory is the previous set, snapshotted per turn; the validator rejects an identical set and nothing else.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persisted intent state, a phase fingerprint from the search parameters, consumed-intent reporting, and REPEATED_CTA_INTENT.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In relative_dates_then_shift, "Show nonstop flights only" was offered on three turns of the same search, and "Show cheapest option" came back right after the traveler asked which option was cheapest.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persist ctaState in context.flight, which already survives snapshotGatewayContext. Compute the fingerprint from route, dates, trip type, cabin and passengers, and validate drafts against the blocked keys.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit: a consumed key is rejected for the rest of the scope, and a generated key is accepted again after the fingerprint changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C - State / context</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A successful prediction is not carried into later turns</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dynamic prompt shows "Successful price prediction available" with the strongest dates (prompt.ts:987). That grounds CTAs such as "Search the strongest predicted date" on later turns (:535).</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flight.lastPricePrediction is stored, but the dynamic instructions show only the route codes (buildPricePredictionRouteSummary in agent.ts).</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A compact summary of the last successful prediction in the dynamic instructions.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After a prediction-only turn the agent cannot offer to search the recommended date on the next turn.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add the strongest dates from lastPricePrediction to the dynamic instructions while its route matches the current one.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit: the dynamic instructions list the strongest dates after a successful prediction and drop them after a route change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - Prompt authority</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content rules forbid CTAs production now allows</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The updated text drops the old mandatory-field guard and bans only empty slot-filling such as "Add departure location" or "Add travel date" (prompt.ts:505). It allows concrete timing and discovery CTAs: "Cheapest next month", "Return after a week", "Make it one way", "Beach getaways from {departure}", "{arrival} travel tips" (:526-538).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLIGHT_PROMPT, written to the earlier text, forbids any request to choose or change dates and limits CTAs to actions Flight can perform. The validator rejects wording such as "travel dates", "date range" and "return date" (BLOCKED_FIELD_WORDING in suggested-questions-tool.ts).</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The slot-filling-only ban, and the discovery and destination-planning CTA families.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The state-matrix CTAs would be refused by the prompt or the validator.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Narrow the prompt rule and the validator to empty slot-filling. Allow destination-planning CTAs, which the Manager routes to Trip Planner when tapped.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit: the validator accepts every example in the production state matrix and still rejects "Add travel date".</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D - Execution flow</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Manager answers pre-search turns without Flight</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local-only</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every Flight turn, including missing-info and clarification turns, ends with the CTA update (prompt.ts:727, "update_flight_suggested_questions alone for missing-info, clarification, source-option, or no-action responses"; :496).</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Manager often collects missing trip details itself. In trip_details_one_at_a_time, "from Delhi" and "going to Mumbai" never reached Flight, so no CTA could be generated even under the new rules.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A path by which every flight-detail turn produces CTAs.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-search CTAs would appear only on turns the Manager happens to delegate.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DECISION NEEDED: have the Manager delegate flight-detail collection to Flight, or generate CTAs for flight-intent turns the Manager answers itself.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live: every turn of trip_details_one_at_a_time with partial context ends with 3 CTAs, whichever agent answered it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1307,7 +1776,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 2026-10-01T12:21:31.639Z</t>
+          <t xml:space="preserve">Generated: 2026-10-01T12:40:29.333Z</t>
         </is>
       </c>
     </row>
@@ -3347,6 +3816,33 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Port the updated production CTA design: the pre-search state matrix, CTA records with intent keys, ctaState with a phase fingerprint and consumed intents, EMPTY_CTA_NOT_ALLOWED and REPEATED_CTA_INTENT, prediction hydration, narrowed content rules, and a CTA path for turns the Manager answers itself</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G19, G20, G21, G22, G23, G24, G25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production changed the design on 2026-10-01 at 18:04, after Steps 1-5 landed. Settle the open questions on the new text first, because they decide the tool contract.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - awaiting go-ahead</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3490,6 +3986,91 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who generates CTAs on turns the Manager answers itself (G25)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-search CTAs need a model call that sees the partial trip. Either the Manager routes every flight-detail turn to Flight, which adds a specialist call to turns it now answers alone, or it generates the CTA records itself for flight-intent turns.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - decide before Step 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: blocking scope of used intents</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Used intents are "blocked for the conversation" (prompt.ts:484, :1007), but the worked example says "neither may appear again in this search phase" (:486). Conversation scope would stop offering "Show non-stop flights" for every later route once it has been used.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - confirm the intended scope with the production owners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: a rejected empty list</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An empty list is allowed when "three safe, distinct actions cannot be grounded" (prompt.ts:470), but the tool rejects [] whenever travel context exists (:474). If the single retry also fails, nothing is stored, so the previous turn's CTAs stay on screen.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - decide whether a final rejection should clear the visible CTAs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: phase-wide blocking of generated intents</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every generated intent stays blocked while the phase fingerprint is unchanged, and the fingerprint leaves out filters (prompt.ts:1006). A long conversation about one search uses up three intents per turn and can run out of good ones.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - consider blocking only the last few turns' generated intents, or adding filters to the fingerprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: leftover search-key re-check</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The routing tail still says the tool "re-checks the latest searchKey at execution time" (prompt.ts:722), though a search key no longer decides whether CTAs are generated.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - remove it from the production text, or define what the re-check now does.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3529,7 +4110,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Fix Sequence: the order the gaps were closed in, with commits. Open Decisions: the choices made along the way, and the one still open.</t>
+          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Fix Sequence: the order the gaps were closed in, with commits. Open Decisions: the choices made along the way, and those still open.</t>
         </is>
       </c>
     </row>
@@ -3548,48 +4129,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line numbers</t>
+          <t xml:space="preserve">Production text versions</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
+          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT was replaced on 2026-10-01 at 18:04 with a CTA-record design. G1-G18, the Production Map and the Chain Map compare against the earlier text, so their production line numbers refer to it. G19-G25 compare against the new text.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measurements</t>
+          <t xml:space="preserve">Line numbers</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
+          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin</t>
+          <t xml:space="preserve">Measurements</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Uncommitted work</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every gap records the commit that closed it in Status. The "Current behavior" column describes the code at analysis time, before those commits. The clearing in flight_search and apply_filter (G10) is still uncommitted working-tree code.</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G1-G18 record the commit that closed them in Status; G19-G25, from the updated production text, are open. The "Current behavior" column describes the code at analysis time. The clearing in flight_search and apply_filter (G10) is still uncommitted working-tree code.</t>
         </is>
       </c>
     </row>

--- a/docs/flight-suggested-questions-gap-analysis.xlsx
+++ b/docs/flight-suggested-questions-gap-analysis.xlsx
@@ -7,9 +7,10 @@
     <sheet name="Skip Scenarios" sheetId="3" r:id="rId3"/>
     <sheet name="Production Map" sheetId="4" r:id="rId4"/>
     <sheet name="Chain Map" sheetId="5" r:id="rId5"/>
-    <sheet name="Fix Sequence" sheetId="6" r:id="rId6"/>
-    <sheet name="Open Decisions" sheetId="7" r:id="rId7"/>
-    <sheet name="Read Me" sheetId="8" r:id="rId8"/>
+    <sheet name="Search Review" sheetId="6" r:id="rId6"/>
+    <sheet name="Fix Sequence" sheetId="7" r:id="rId7"/>
+    <sheet name="Open Decisions" sheetId="8" r:id="rId8"/>
+    <sheet name="Read Me" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -1348,7 +1349,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 3915f3b and 047f9cd</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1415,7 +1416,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 3915f3b</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1482,7 +1483,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Addressed in the prompt (3915f3b): sameness is judged by intent; intent-key records not adopted</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1549,7 +1550,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Partly fixed in 3915f3b: suggestions used on the previous turn are blocked; no persisted intent state, so older ones can return in Manager mode</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1616,7 +1617,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 3915f3b</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1683,7 +1684,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 3915f3b and 047f9cd</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1750,7 +1751,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open</t>
+          <t xml:space="preserve">Fixed in 3915f3b, scoped in a340ee2: the Manager sends partial flight details to Flight</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1776,7 +1777,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 2026-10-01T12:40:29.333Z</t>
+          <t xml:space="preserve">Generated: 2026-10-01T14:21:43.876Z</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1791,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recorded turns: 213. Turns where Flight ran: 194. Turns the Manager answered without Flight: 19 - excluded below, because Flight never ran and so could not skip the tool. Manager-path turns: 213 of 213.</t>
+          <t xml:space="preserve">Recorded turns: 213. Turns where Flight ran: 197. Turns the Manager answered without Flight: 16 - excluded below, because Flight never ran and so could not skip the tool. Manager-path turns: 213 of 213.</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1854,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">119</t>
+          <t xml:space="preserve">118</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">94</t>
+          <t xml:space="preserve">93</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1875,17 +1876,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">79</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">36%</t>
+          <t xml:space="preserve">39%</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1945,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter</t>
+          <t xml:space="preserve">getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1954,19 +1955,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">62%</t>
+          <t xml:space="preserve">35%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext</t>
+          <t xml:space="preserve">apply_filter</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1976,12 +1977,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">33%</t>
+          <t xml:space="preserve">61%</t>
         </is>
       </c>
     </row>
@@ -1993,46 +1994,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">27%</t>
+          <t xml:space="preserve">43%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter + flight_search</t>
+          <t xml:space="preserve">price_prediction_tool</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">89%</t>
+          <t xml:space="preserve">40%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_prediction_tool</t>
+          <t xml:space="preserve">apply_filter + flight_search</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2042,12 +2043,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">33%</t>
+          <t xml:space="preserve">89%</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2060,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2081,108 +2082,108 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">33%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t xml:space="preserve">flight_search + price_prediction_tool</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">0%</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call rate by core-tool signature - flight-conversation-* scripted conversations only (the set fix verification re-runs)</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core tools in the turn</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flight turns</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool called</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate</t>
+          <t xml:space="preserve">Call rate by core-tool signature - flight-conversation-* scripted conversations only (the set fix verification re-runs)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">apply_filter</t>
+          <t xml:space="preserve">Core tools in the turn</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search</t>
+          <t xml:space="preserve">apply_filter</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2194,17 +2195,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext</t>
+          <t xml:space="preserve">flight_search</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2216,17 +2217,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no tool)</t>
+          <t xml:space="preserve">getGeneratedContractsContext</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2238,17 +2239,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">price_prediction_tool</t>
+          <t xml:space="preserve">(no tool)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2260,17 +2261,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
+          <t xml:space="preserve">price_prediction_tool</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2304,307 +2305,312 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight_search + getGeneratedContractsContext</t>
+          <t xml:space="preserve">getGeneratedContractsContext + price_prediction_tool</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">apply_filter + getGeneratedContractsContext</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call rate by artifact group</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Group</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Recorded turns</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flight turns</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tool called</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Search/filter turns with no refresh</t>
+          <t xml:space="preserve">Call rate by artifact group</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">flight-conversation-*</t>
+          <t xml:space="preserve">Group</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">Recorded turns</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">Flight turns</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">66</t>
+          <t xml:space="preserve">Tool called</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">Rate</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Search/filter turns with no refresh</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">manager-flight-*</t>
+          <t xml:space="preserve">flight-conversation-*</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">88</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">45%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">manager-realistic-*</t>
+          <t xml:space="preserve">manager-flight-*</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">93</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t xml:space="preserve">88</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t xml:space="preserve">40</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45%</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38%</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t xml:space="preserve">manager-realistic-*</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t xml:space="preserve">TOTAL</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t xml:space="preserve">213</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62%</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Before and after 73d5033 - scripted conversations recorded on both sides, Flight turns</t>
-        </is>
-      </c>
-    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turns that called the tool</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Before (artifacts/before-suggestions-mandate)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After (re-recorded runs)</t>
+          <t xml:space="preserve">Before and after 73d5033 - scripted conversations recorded on both sides, Flight turns</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns</t>
+          <t xml:space="preserve">Turns that called the tool</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 of 58 (53%)</t>
+          <t xml:space="preserve">Before (artifacts/before-suggestions-mandate)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">64 of 64 (100%)</t>
+          <t xml:space="preserve">After (re-recorded runs)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ran flight_search or apply_filter</t>
+          <t xml:space="preserve">All Flight turns</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 of 36 (86%)</t>
+          <t xml:space="preserve">31 of 58 (53%)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">40 of 40 (100%)</t>
+          <t xml:space="preserve">65 of 65 (100%)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ran neither</t>
+          <t xml:space="preserve">Ran flight_search or apply_filter</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 of 22 (0%)</t>
+          <t xml:space="preserve">31 of 36 (86%)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 of 24 (100%)</t>
+          <t xml:space="preserve">39 of 39 (100%)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contract read only</t>
+          <t xml:space="preserve">Ran neither</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 of 11 (0%)</t>
+          <t xml:space="preserve">0 of 22 (0%)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 of 16 (100%)</t>
+          <t xml:space="preserve">26 of 26 (100%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Price prediction only</t>
+          <t xml:space="preserve">Contract read only</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 of 5 (0%)</t>
+          <t xml:space="preserve">0 of 11 (0%)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 of 3 (100%)</t>
+          <t xml:space="preserve">17 of 17 (100%)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">No core tool</t>
+          <t xml:space="preserve">Price prediction only</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2614,54 +2620,71 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 of 2 (100%)</t>
+          <t xml:space="preserve">4 of 4 (100%)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search/filter turns with no refresh</t>
+          <t xml:space="preserve">No core tool</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">0 of 5 (0%)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">3 of 3 (100%)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Search/filter turns with no refresh</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Turns passing the runner’s suggestions check: the update ran last, with 3 suggestions when a search existed and none otherwise</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t xml:space="preserve">not recorded</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64 of 64</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Target after the fix</t>
-        </is>
-      </c>
-    </row>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65 of 65</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target after the fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">Every core-tool signature row reaches 100%, including getGeneratedContractsContext, price_prediction_tool and (no tool), and "Search/filter turns with no refresh" reaches 0.</t>
         </is>
@@ -2704,7 +2727,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 17 of 51 called it. Scripted conversations: 16 of 16.</t>
+          <t xml:space="preserve">All Flight turns: 18 of 52 called it. Scripted conversations: 17 of 17.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2726,7 +2749,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 3 of 9 called it. Scripted conversations: 3 of 3.</t>
+          <t xml:space="preserve">All Flight turns: 4 of 10 called it. Scripted conversations: 4 of 4.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2748,7 +2771,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 3 of 11 called it. Scripted conversations: 3 of 3.</t>
+          <t xml:space="preserve">All Flight turns: 6 of 14 called it. Scripted conversations: 6 of 6.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2770,7 +2793,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">All Flight turns: 32 of 52 called it. Scripted conversations: 20 of 20.</t>
+          <t xml:space="preserve">All Flight turns: 31 of 51 called it. Scripted conversations: 19 of 19.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2968,7 +2991,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 of 213 recorded turns.</t>
+          <t xml:space="preserve">16 of 213 recorded turns.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3603,243 +3626,352 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step</t>
+          <t xml:space="preserve">Area</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scope</t>
+          <t xml:space="preserve">Production rule (FLIGHT_PROD_PROMPT_TEXT, updated text)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Local handling</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why this order</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status</t>
+          <t xml:space="preserve">Verdict</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 0</t>
+          <t xml:space="preserve">Blocking details</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This Excel register + extract the shared XLSX writer into scripts/lib/xlsx-workbook.ts</t>
+          <t xml:space="preserve">Departure, arrival and outbound date block a search; a detail is missing only if absent from the latest message, the existing parameters and the history.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Evidence priority across four levels, checked before any question (FLIGHT_PROMPT, "Evidence priority and request assembly").</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Track the gaps before changing behaviour.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done in 5f32c14, a5de88c and 9f2a010</t>
+          <t xml:space="preserve">Covered</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 0b</t>
+          <t xml:space="preserve">When to search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baseline: re-run the ten scripted conversations on the current prompt, then re-run this generator</t>
+          <t xml:space="preserve">Call flight_search as soon as all three are known; any route, date, passenger, trip-type or cabin change starts a new search.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">Same rule in the flight_search section, plus "do not start a new search solely because route and date are available".</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">No recorded artifact reflects the working-tree prompt, so later steps need a fresh baseline to compare against. Live runs cost API calls.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Replaced by the scripted runs recorded earlier on 2026-10-01, kept in artifacts/before-suggestions-mandate/ (see Evidence)</t>
+          <t xml:space="preserve">Covered</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 1</t>
+          <t xml:space="preserve">Partial updates</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deterministic state correctness: per-turn written flag, turn-end finalize on the success and error paths of both the standalone and Manager runs, per-turn logging on the Manager path</t>
+          <t xml:space="preserve">The latest message overrides only the fields it mentions; a route-only change keeps the dates.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9, G10, G11, G13</t>
+          <t xml:space="preserve">Same, stated for routes, dates, passengers, trip type and cabin.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correct on its own merits: after this, a skipped call can no longer ship stale data. Decide the read-only skip policy first. Shipped alone it leaves no suggestions on most read-only turns, so land it with or just before Steps 2-3.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done in 73d5033, together with Steps 2-4</t>
+          <t xml:space="preserve">Covered</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 2</t>
+          <t xml:space="preserve">Defaults</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tool contract: required-terminal description, schema decision, per-run gate with one retry, per-Flight-run turn state, optional content validator</t>
+          <t xml:space="preserve">One-way, 1 adult, economy; a return date makes it a round trip.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6, G7, G8, G16, G17</t>
+          <t xml:space="preserve">Same safe defaults.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The tool description must stop contradicting the mandate before the prompt asserts it.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done in 73d5033</t>
+          <t xml:space="preserve">Covered</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 3</t>
+          <t xml:space="preserve">Round trip without return</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prompt authority: mandate wording, stop rule, adapted chain list, checklist line, Manager-mode ordering, content rules, active-search binding</t>
+          <t xml:space="preserve">Ask only for return timing or duration.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1, G2, G3, G4, G5, G15, G18</t>
+          <t xml:space="preserve">Same; a stated stay length derives the return date.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Raises the call rate once the state layer is already safe.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done in 73d5033</t>
+          <t xml:space="preserve">Covered</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 4</t>
+          <t xml:space="preserve">Passenger and cabin inference</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tests: flip flight-agent-price-prediction.test.ts:609-612, invert NON_CORE_TOOLS, rewrite the flight-gap-contracts case, add the tool to the 17 expectedTools arrays, add an npm script for the variation live check</t>
+          <t xml:space="preserve">"we" or "2 people" sets adults; "cheaper" or "budget" sets economy.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">G12</t>
+          <t xml:space="preserve">Never infers a count from "we" and never downgrades an established cabin for "cheaper".</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Must land with Step 3: the unit suite asserts the optional wording, and the report harness compares tool sequences by exact equality.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done in 73d5033, 4dae460 and 488c0e9</t>
+          <t xml:space="preserve">Local kept: stricter</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 5</t>
+          <t xml:space="preserve">Multi-city</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconcile the four docs</t>
+          <t xml:space="preserve">Only when explicitly requested.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">G14</t>
+          <t xml:space="preserve">Same.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Last, once behaviour is settled.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Done in 488c0e9: docs/flight-suggested-questions.md is the current reference</t>
+          <t xml:space="preserve">Covered</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step 6</t>
+          <t xml:space="preserve">Search plus filters</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Port the updated production CTA design: the pre-search state matrix, CTA records with intent keys, ctaState with a phase fingerprint and consumed intents, EMPTY_CTA_NOT_ALLOWED and REPEATED_CTA_INTENT, prediction hydration, narrowed content rules, and a CTA path for turns the Manager answers itself</t>
+          <t xml:space="preserve">flight_search then apply_filter; never claim an unapplied filter; pending filters apply after the search.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">G19, G20, G21, G22, G23, G24, G25</t>
+          <t xml:space="preserve">Same, plus pending filters preserved across clarification turns and carried by the Manager.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production changed the design on 2026-10-01 at 18:04, after Steps 1-5 landed. Settle the open questions on the new text first, because they decide the tool contract.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - awaiting go-ahead</t>
+          <t xml:space="preserve">Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vague timing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolve_flight_date resolves it, the search uses its date, and a later route-only turn reuses it.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dates derived from the turn clock with the same week, weekend, month and year rules, and the interval is preserved across route-only or duration-only replies.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Covered, adapted: no resolver tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prediction then search</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After a successful prediction, search its first date when results were requested; after a failure, search once on a usable date.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same, with the failure fallback restricted to a date inside the traveler's allowed interval.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Searching a recommended date later</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The hydrated prediction lets a later turn search the strongest date.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The dynamic instructions now show the last successful prediction (3915f3b).</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed (G23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter before any search</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ask for route and date.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MISSING_SEARCH with complete intent runs the search, then the filter; otherwise asks only for what is missing.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local kept: stronger</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Invalid dates</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct the date and retry once silently.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Never shifts an exact user date; retries only with retry-safe feedback, otherwise asks one narrow question.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local kept: safer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Searches started from suggestions</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Search this trip", "Search flights next weekend", "Return after a week", "Make it one way" and "Search the strongest predicted date" lead to searches.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Each lands on an existing search or date rule; the predicted date comes from the new prediction summary.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turns the Manager answered alone</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A single agent sees every flight turn.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Manager now sends partial flight details to Flight (3915f3b), so detail-collection turns reach the search logic.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed (G25)</t>
         </is>
       </c>
     </row>
@@ -3853,221 +3985,243 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topic</t>
+          <t xml:space="preserve">Step</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detail</t>
+          <t xml:space="preserve">Scope</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner / status</t>
+          <t xml:space="preserve">Gaps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why this order</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who renders the suggestions?</t>
+          <t xml:space="preserve">Step 0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">context.flight.suggestedQuestions is persisted with the chat’s runtime context (api/chat/orchestrator.ts:191) and emitted in the SSE done.flightContext payload (:228). public/chat-dashboard reads flightContext for showFlight and searchResults but has zero references to suggestions. The only in-repo reader is the Flight agent’s own next-turn prompt (agent.ts:109-116, 212-214), as anti-repeat input. Restoring the mandate buys production parity and correct state plus about one extra model call per Flight turn, but no user-visible change until a renderer exists.</t>
+          <t xml:space="preserve">This Excel register + extract the shared XLSX writer into scripts/lib/xlsx-workbook.ts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - confirm the real consumer (presumably the CheapOair mobile client).</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Track the gaps before changing behaviour.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 5f32c14, a5de88c and 9f2a010</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7 schema shape</t>
+          <t xml:space="preserve">Step 0b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A plain .min(3) breaks the empty-array clear path. Option (b) - exactly 3 at the schema level, clearing moved to the Step 1 finalize - is preferred.</t>
+          <t xml:space="preserve">Baseline: re-run the ten scripted conversations on the current prompt, then re-run this generator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved in 73d5033 - kept 0..3 and made the first rejection retry-safe instead. The update now runs on every turn, so the empty array stays the no-search signal, and tool feedback corrects a misjudged search state instead of ending the turn. A second rejection withdraws the tool.</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No recorded artifact reflects the working-tree prompt, so later steps need a fresh baseline to compare against. Live runs cost API calls.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Replaced by the scripted runs recorded earlier on 2026-10-01, kept in artifacts/before-suggestions-mandate/ (see Evidence)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dead reference prompt</t>
+          <t xml:space="preserve">Step 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT (prompt.ts:148-995) carries all the mandatory language. It is commented "Historical comparison reference only; never included in runtime instructions" (:147), exists only in the uncommitted working tree, and no runtime or test code imports it: agent.ts:11 imports only FLIGHT_PROMPT. Lines 914-995 are a captured production dynamic block. scripts/audit-session-prompts.ts:58 states the invariant: "FLIGHT_PROMPT is the single authoritative runtime prompt."</t>
+          <t xml:space="preserve">Deterministic state correctness: per-turn written flag, turn-end finalize on the success and error paths of both the standalone and Manager runs, per-turn logging on the Manager path</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved - do not edit that string; every rule must land in the live prompt.</t>
+          <t xml:space="preserve">G9, G10, G11, G13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct on its own merits: after this, a skipped call can no longer ship stale data. Decide the read-only skip policy first. Shipped alone it leaves no suggestions on most read-only turns, so land it with or just before Steps 2-3.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033, together with Steps 2-4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skip policy on read-only turns</t>
+          <t xml:space="preserve">Step 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">When Flight skips the tool on a turn that ran no search or filter, the previous suggestions still describe the same results. Clearing them, as the draft finalize and Trip Planner do, removes any risk of suggesting what the user just did, but leaves no suggestions on most read-only turns until Steps 2-3 raise the call rate. Keeping them leaves suggestions that can repeat the action just taken.</t>
+          <t xml:space="preserve">Tool contract: required-terminal description, schema decision, per-run gate with one retry, per-Flight-run turn state, optional content validator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved in 73d5033 - clear, shipped together with the mandate, so a skip leaves no suggestions rather than stale ones.</t>
+          <t xml:space="preserve">G6, G7, G8, G16, G17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tool description must stop contradicting the mandate before the prompt asserts it.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turns where Flight never runs</t>
+          <t xml:space="preserve">Step 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">When the Manager answers without calling flight_agent, nothing touches context.flight.suggestedQuestions, and the previous Flight suggestions go out again in done.flightContext (api/chat/orchestrator.ts:228). They still describe the active search, but not the latest exchange. The Evidence sheet counts these turns separately.</t>
+          <t xml:space="preserve">Prompt authority: mandate wording, stop rule, adapted chain list, checklist line, Manager-mode ordering, content rules, active-search binding</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved in 73d5033 - keep. The finalize clears only after a Flight run; a turn the Manager answers alone leaves the suggestions for the active search. Revisit if the client should hide them on such turns.</t>
+          <t xml:space="preserve">G1, G2, G3, G4, G5, G15, G18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raises the call rate once the state layer is already safe.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uncommitted Step 1 draft</t>
+          <t xml:space="preserve">Step 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">suggested-questions-tool.ts (writtenRequestIds, finalizeFlightSuggestedQuestions), runner.ts and manager/specialists/flight.ts were edited at 15:31-15:32 on 2026-10-01, after this register was first committed. The draft is uncommitted and untested. Known holes: no finalize when the nested Flight run throws on the Manager path, and logging only in the standalone runner.</t>
+          <t xml:space="preserve">Tests: flip flight-agent-price-prediction.test.ts:609-612, invert NON_CORE_TOOLS, rewrite the flight-gap-contracts case, add the tool to the 17 expectedTools arrays, add an npm script for the variation live check</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved in 73d5033 - reworked and committed: a turn snapshot of the previous suggestions, finalize at the end of the Manager turn in a finally, and an agent_start mark for Flight runs.</t>
+          <t xml:space="preserve">G12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Must land with Step 3: the unit suite asserts the optional wording, and the report harness compares tool sequences by exact equality.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 73d5033, 4dae460 and 488c0e9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">G16 scope</t>
+          <t xml:space="preserve">Step 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production never validated suggestion content in code, so a validator goes beyond parity. It matches Trip Planner, which validates and allows one retry.</t>
+          <t xml:space="preserve">Reconcile the four docs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved in 73d5033 - in scope: the tool validates drafts and allows one corrected retry.</t>
+          <t xml:space="preserve">G14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last, once behaviour is settled.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 488c0e9: docs/flight-suggested-questions.md is the current reference</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who generates CTAs on turns the Manager answers itself (G25)</t>
+          <t xml:space="preserve">Step 6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-search CTAs need a model call that sees the partial trip. Either the Manager routes every flight-detail turn to Flight, which adds a specialist call to turns it now answers alone, or it generates the CTA records itself for flight-intent turns.</t>
+          <t xml:space="preserve">Port the updated production CTA design: the pre-search state matrix, CTA records with intent keys, ctaState with a phase fingerprint and consumed intents, EMPTY_CTA_NOT_ALLOWED and REPEATED_CTA_INTENT, prediction hydration, narrowed content rules, and a CTA path for turns the Manager answers itself</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open - decide before Step 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Updated production text: blocking scope of used intents</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Used intents are "blocked for the conversation" (prompt.ts:484, :1007), but the worked example says "neither may appear again in this search phase" (:486). Conversation scope would stop offering "Show non-stop flights" for every later route once it has been used.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - confirm the intended scope with the production owners.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Updated production text: a rejected empty list</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An empty list is allowed when "three safe, distinct actions cannot be grounded" (prompt.ts:470), but the tool rejects [] whenever travel context exists (:474). If the single retry also fails, nothing is stored, so the previous turn's CTAs stay on screen.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - decide whether a final rejection should clear the visible CTAs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Updated production text: phase-wide blocking of generated intents</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Every generated intent stays blocked while the phase fingerprint is unchanged, and the fingerprint leaves out filters (prompt.ts:1006). A long conversation about one search uses up three intents per turn and can run out of good ones.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - consider blocking only the last few turns' generated intents, or adding filters to the fingerprint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Updated production text: leftover search-key re-check</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The routing tail still says the tool "re-checks the latest searchKey at execution time" (prompt.ts:722), though a search key no longer decides whether CTAs are generated.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open - remove it from the production text, or define what the re-check now does.</t>
+          <t xml:space="preserve">G19, G20, G21, G22, G23, G24, G25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production changed the design on 2026-10-01 at 18:04, after Steps 1-5 landed. Settle the open questions on the new text first, because they decide the tool contract.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done in 3915f3b, 5625dd8, 047f9cd and a340ee2; G21 and G22 only partly, by design</t>
         </is>
       </c>
     </row>
@@ -4089,100 +4243,328 @@
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner / status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">What this is</t>
+          <t xml:space="preserve">Who renders the suggestions?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tracking register for the update_flight_suggested_questions gap between production (FLIGHT_PROD_PROMPT_TEXT, src/agents/flight/prompt.ts:148-995, reference text that never reaches the model) and the local Flight Agent (FLIGHT_PROMPT, the dynamic instructions in agent.ts, the tool, and both runners).</t>
+          <t xml:space="preserve">context.flight.suggestedQuestions is persisted with the chat’s runtime context (api/chat/orchestrator.ts:191) and emitted in the SSE done.flightContext payload (:228). public/chat-dashboard reads flightContext for showFlight and searchResults but has zero references to suggestions. The only in-repo reader is the Flight agent’s own next-turn prompt (agent.ts:109-116, 212-214), as anti-repeat input. Restoring the mandate buys production parity and correct state plus about one extra model call per Flight turn, but no user-visible change until a renderer exists.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open - confirm the real consumer (presumably the CheapOair mobile client).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sheets</t>
+          <t xml:space="preserve">G7 schema shape</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Fix Sequence: the order the gaps were closed in, with commits. Open Decisions: the choices made along the way, and those still open.</t>
+          <t xml:space="preserve">A plain .min(3) breaks the empty-array clear path. Option (b) - exactly 3 at the schema level, clearing moved to the Step 1 finalize - is preferred.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved in 73d5033 - kept 0..3 and made the first rejection retry-safe instead. The update now runs on every turn, so the empty array stays the no-search signal, and tool feedback corrects a misjudged search state instead of ending the turn. A second rejection withdraws the tool.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">How to update</t>
+          <t xml:space="preserve">Dead reference prompt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edit scripts/write-suggested-questions-gap-register.ts, then run npm run gaps:suggested-questions. The generator rewrites this workbook, so edits made here are lost. When a fix lands, change that gap’s status in the generator and commit the generator and the workbook together.</t>
+          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT (prompt.ts:148-995) carries all the mandatory language. It is commented "Historical comparison reference only; never included in runtime instructions" (:147), exists only in the uncommitted working tree, and no runtime or test code imports it: agent.ts:11 imports only FLIGHT_PROMPT. Lines 914-995 are a captured production dynamic block. scripts/audit-session-prompts.ts:58 states the invariant: "FLIGHT_PROMPT is the single authoritative runtime prompt."</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved - do not edit that string; every rule must land in the live prompt.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production text versions</t>
+          <t xml:space="preserve">Skip policy on read-only turns</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT was replaced on 2026-10-01 at 18:04 with a CTA-record design. G1-G18, the Production Map and the Chain Map compare against the earlier text, so their production line numbers refer to it. G19-G25 compare against the new text.</t>
+          <t xml:space="preserve">When Flight skips the tool on a turn that ran no search or filter, the previous suggestions still describe the same results. Clearing them, as the draft finalize and Trip Planner do, removes any risk of suggesting what the user just did, but leaves no suggestions on most read-only turns until Steps 2-3 raise the call rate. Keeping them leaves suggestions that can repeat the action just taken.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved in 73d5033 - clear, shipped together with the mandate, so a skip leaves no suggestions rather than stale ones.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line numbers</t>
+          <t xml:space="preserve">Turns where Flight never runs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
+          <t xml:space="preserve">When the Manager answers without calling flight_agent, nothing touches context.flight.suggestedQuestions, and the previous Flight suggestions go out again in done.flightContext (api/chat/orchestrator.ts:228). They still describe the active search, but not the latest exchange. The Evidence sheet counts these turns separately.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved in 73d5033 - keep. The finalize clears only after a Flight run; a turn the Manager answers alone leaves the suggestions for the active search. Revisit if the client should hide them on such turns.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Measurements</t>
+          <t xml:space="preserve">Uncommitted Step 1 draft</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
+          <t xml:space="preserve">suggested-questions-tool.ts (writtenRequestIds, finalizeFlightSuggestedQuestions), runner.ts and manager/specialists/flight.ts were edited at 15:31-15:32 on 2026-10-01, after this register was first committed. The draft is uncommitted and untested. Known holes: no finalize when the nested Flight run throws on the Manager path, and logging only in the standalone runner.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved in 73d5033 - reworked and committed: a turn snapshot of the previous suggestions, finalize at the end of the Manager turn in a finally, and an agent_start mark for Flight runs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Origin</t>
+          <t xml:space="preserve">G16 scope</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+          <t xml:space="preserve">Production never validated suggestion content in code, so a validator goes beyond parity. It matches Trip Planner, which validates and allows one retry.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved in 73d5033 - in scope: the tool validates drafts and allows one corrected retry.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Who generates CTAs on turns the Manager answers itself (G25)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-search CTAs need a model call that sees the partial trip. Either the Manager routes every flight-detail turn to Flight, which adds a specialist call to turns it now answers alone, or it generates the CTA records itself for flight-intent turns.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved in 3915f3b - the Manager prompt now sends any reply that supplies part of a flight request to Flight. Live: "from Delhi" and "going to Mumbai" both reached Flight and got grounded suggestions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: blocking scope of used intents</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Used intents are "blocked for the conversation" (prompt.ts:484, :1007), but the worked example says "neither may appear again in this search phase" (:486). Conversation scope would stop offering "Show non-stop flights" for every later route once it has been used.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved locally in 3915f3b - blocked while the trip is unchanged, matching the worked example. Still worth confirming with the production owners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: a rejected empty list</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An empty list is allowed when "three safe, distinct actions cannot be grounded" (prompt.ts:470), but the tool rejects [] whenever travel context exists (:474). If the single retry also fails, nothing is stored, so the previous turn's CTAs stay on screen.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved locally - after a final rejection the turn-end finalize clears the unwritten suggestions, so nothing stale stays on screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: phase-wide blocking of generated intents</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every generated intent stays blocked while the phase fingerprint is unchanged, and the fingerprint leaves out filters (prompt.ts:1006). A long conversation about one search uses up three intents per turn and can run out of good ones.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolved locally in 3915f3b - not adopted. Only the previous turn's set is compared, which cannot run out of suggestions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated production text: leftover search-key re-check</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The routing tail still says the tool "re-checks the latest searchKey at execution time" (prompt.ts:722), though a search key no longer decides whether CTAs are generated.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not applicable locally - the local prompt never had that line. Worth removing from the production text.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What this is</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tracking register for the update_flight_suggested_questions gap between production (FLIGHT_PROD_PROMPT_TEXT, src/agents/flight/prompt.ts:148-995, reference text that never reaches the model) and the local Flight Agent (FLIGHT_PROMPT, the dynamic instructions in agent.ts, the tool, and both runners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheets</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gap Register: one row per gap. Evidence: call rates measured from artifacts/. Skip Scenarios: when the current agent skips the tool. Production Map: where production states the mandate, beside the local equivalent. Chain Map: production’s 15 tool chains mapped to the five registered local tools. Search Review: production’s flight_search rules against the local prompt. Fix Sequence: the order the gaps were closed in, with commits. Open Decisions: the choices made along the way, and those still open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How to update</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edit scripts/write-suggested-questions-gap-register.ts, then run npm run gaps:suggested-questions. The generator rewrites this workbook, so edits made here are lost. When a fix lands, change that gap’s status in the generator and commit the generator and the workbook together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production text versions</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLIGHT_PROD_PROMPT_TEXT was replaced on 2026-10-01 at 18:04 with a CTA-record design. G1-G18, the Production Map and the Chain Map compare against the earlier text, so their production line numbers refer to it. G19-G25 compare against the new text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Line numbers</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file:line references point at the working tree on 2026-10-01, including uncommitted changes. Symbol names are given where lines are likely to move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measurements</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Evidence sheet and the measured Skip Scenarios rows are re-tallied from artifacts/ on every run. Text marked "At analysis" quotes the numbers from 2026-10-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Origin</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production regression: production stated the rule and the local agent dropped or contradicted it. Local-only: introduced locally. Shared weakness: production had the same code or wording, but its per-turn mandate masked it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Uncommitted work</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1-G18 record the commit that closed them in Status; G19-G25, from the updated production text, are open. The "Current behavior" column describes the code at analysis time. The clearing in flight_search and apply_filter (G10) is still uncommitted working-tree code.</t>
+          <t xml:space="preserve">Every gap records the commits that closed it in Status; G21 and G22 are only partly closed, by design. The "Current behavior" column describes the code at analysis time. The clearing in flight_search and apply_filter (G10) is still uncommitted working-tree code.</t>
         </is>
       </c>
     </row>

--- a/docs/flight-suggested-questions-gap-analysis.xlsx
+++ b/docs/flight-suggested-questions-gap-analysis.xlsx
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed in 3915f3b and 047f9cd</t>
+          <t xml:space="preserve">Fixed in 3915f3b, 047f9cd and c02b4d9</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 2026-10-01T14:21:43.876Z</t>
+          <t xml:space="preserve">Generated: 2026-10-01T14:29:46.108Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done in 3915f3b, 5625dd8, 047f9cd and a340ee2; G21 and G22 only partly, by design</t>
+          <t xml:space="preserve">Done in 3915f3b, 5625dd8, 047f9cd, a340ee2 and c02b4d9; G21 and G22 only partly, by design</t>
         </is>
       </c>
     </row>
